--- a/AAII_Financials/Quarterly/AMTD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMTD_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
   <si>
     <t>AMTD</t>
   </si>
@@ -656,185 +656,192 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44742</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44377</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44104</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43830</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43738</v>
-      </c>
-      <c r="M7" s="2">
-        <v>43646</v>
       </c>
       <c r="N7" s="2">
         <v>43646</v>
       </c>
       <c r="O7" s="2">
+        <v>43646</v>
+      </c>
+      <c r="P7" s="2">
         <v>43555</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43465</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43373</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43281</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43190</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43100</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43008</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>42916</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>42825</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>42735</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>58900</v>
+        <v>135500</v>
       </c>
       <c r="E8" s="3">
-        <v>75500</v>
+        <v>459800</v>
       </c>
       <c r="F8" s="3">
-        <v>42900</v>
+        <v>75200</v>
       </c>
       <c r="G8" s="3">
-        <v>66600</v>
+        <v>335000</v>
       </c>
       <c r="H8" s="3">
-        <v>19900</v>
+        <v>519300</v>
       </c>
       <c r="I8" s="3">
-        <v>10800</v>
+        <v>155300</v>
       </c>
       <c r="J8" s="3">
+        <v>83900</v>
+      </c>
+      <c r="K8" s="3">
         <v>69100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>25000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1491000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1451000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1516000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1398000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1382000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1415000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1257000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>983000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>931000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>904000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>859000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>830000</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -868,18 +875,18 @@
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="3">
         <v>59000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>53000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>49000</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -904,8 +911,11 @@
       <c r="Y9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -939,18 +949,18 @@
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="3">
         <v>1432000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1398000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1467000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -975,8 +985,11 @@
       <c r="Y10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,8 +1015,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1073,8 +1087,11 @@
       <c r="Y12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,16 +1161,19 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>500</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
+        <v>3900</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
@@ -1161,11 +1181,11 @@
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3">
-        <v>2200</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
+        <v>17100</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>5</v>
@@ -1179,44 +1199,47 @@
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3">
         <v>-60000</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>1000</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>1000</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1251,43 +1274,46 @@
         <v>0</v>
       </c>
       <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
         <v>69000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>67000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>66000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>70000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>69000</v>
-      </c>
-      <c r="S15" s="3">
-        <v>72000</v>
       </c>
       <c r="T15" s="3">
         <v>72000</v>
       </c>
       <c r="U15" s="3">
+        <v>72000</v>
+      </c>
+      <c r="V15" s="3">
         <v>50000</v>
-      </c>
-      <c r="V15" s="3">
-        <v>44000</v>
       </c>
       <c r="W15" s="3">
         <v>44000</v>
       </c>
       <c r="X15" s="3">
+        <v>44000</v>
+      </c>
+      <c r="Y15" s="3">
         <v>43000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>45000</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1336,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4900</v>
+        <v>22800</v>
       </c>
       <c r="E17" s="3">
+        <v>38600</v>
+      </c>
+      <c r="F17" s="3">
         <v>15300</v>
       </c>
-      <c r="F17" s="3">
-        <v>12100</v>
-      </c>
       <c r="G17" s="3">
-        <v>10900</v>
+        <v>94500</v>
       </c>
       <c r="H17" s="3">
-        <v>4500</v>
+        <v>84900</v>
       </c>
       <c r="I17" s="3">
-        <v>6600</v>
+        <v>34700</v>
       </c>
       <c r="J17" s="3">
+        <v>51500</v>
+      </c>
+      <c r="K17" s="3">
         <v>16500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7300</v>
-      </c>
-      <c r="L17" s="3">
-        <v>6900</v>
       </c>
       <c r="M17" s="3">
         <v>6900</v>
       </c>
       <c r="N17" s="3">
+        <v>6900</v>
+      </c>
+      <c r="O17" s="3">
         <v>711000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>746000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>720000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>764000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>751000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1019000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>921000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>622000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>538000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>546000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>506000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>546000</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>54000</v>
+        <v>112700</v>
       </c>
       <c r="E18" s="3">
-        <v>60100</v>
+        <v>421200</v>
       </c>
       <c r="F18" s="3">
-        <v>30800</v>
+        <v>59900</v>
       </c>
       <c r="G18" s="3">
-        <v>55700</v>
+        <v>240500</v>
       </c>
       <c r="H18" s="3">
-        <v>15500</v>
+        <v>434400</v>
       </c>
       <c r="I18" s="3">
-        <v>4200</v>
+        <v>120600</v>
       </c>
       <c r="J18" s="3">
+        <v>32400</v>
+      </c>
+      <c r="K18" s="3">
         <v>52600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>18200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>780000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>705000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>796000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>634000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>631000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>396000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>336000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>361000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>393000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>358000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>353000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>284000</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,65 +1512,66 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>9400</v>
+        <v>3800</v>
       </c>
       <c r="E20" s="3">
-        <v>51900</v>
+        <v>73400</v>
       </c>
       <c r="F20" s="3">
-        <v>50500</v>
+        <v>51700</v>
       </c>
       <c r="G20" s="3">
-        <v>35200</v>
+        <v>394300</v>
       </c>
       <c r="H20" s="3">
-        <v>41000</v>
+        <v>274800</v>
       </c>
       <c r="I20" s="3">
-        <v>13500</v>
+        <v>319500</v>
       </c>
       <c r="J20" s="3">
+        <v>105400</v>
+      </c>
+      <c r="K20" s="3">
         <v>4500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>36500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>14800</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>14000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2000</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-13000</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1550,8 +1584,11 @@
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1576,115 +1613,118 @@
       <c r="J21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L21" s="3">
         <v>15300</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="3">
         <v>849000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>772000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>876000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>706000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>700000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>468000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>395000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>411000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>437000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>402000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>396000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>329000</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>500</v>
+        <v>3600</v>
       </c>
       <c r="E22" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3">
-        <v>800</v>
-      </c>
       <c r="G22" s="3">
-        <v>800</v>
+        <v>6400</v>
       </c>
       <c r="H22" s="3">
-        <v>500</v>
+        <v>6400</v>
       </c>
       <c r="I22" s="3">
-        <v>400</v>
+        <v>3900</v>
       </c>
       <c r="J22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K22" s="3">
         <v>1900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1500</v>
-      </c>
-      <c r="L22" s="3">
-        <v>700</v>
       </c>
       <c r="M22" s="3">
         <v>700</v>
       </c>
       <c r="N22" s="3">
-        <v>37000</v>
+        <v>700</v>
       </c>
       <c r="O22" s="3">
         <v>37000</v>
       </c>
       <c r="P22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>32000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>27000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>28000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>24000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>20000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>23000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>20000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>14000</v>
       </c>
       <c r="X22" s="3">
         <v>14000</v>
@@ -1692,150 +1732,159 @@
       <c r="Y22" s="3">
         <v>14000</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>62900</v>
+        <v>113000</v>
       </c>
       <c r="E23" s="3">
-        <v>111700</v>
+        <v>490400</v>
       </c>
       <c r="F23" s="3">
-        <v>80600</v>
+        <v>111300</v>
       </c>
       <c r="G23" s="3">
-        <v>90100</v>
+        <v>628400</v>
       </c>
       <c r="H23" s="3">
-        <v>55900</v>
+        <v>702800</v>
       </c>
       <c r="I23" s="3">
-        <v>17300</v>
+        <v>436100</v>
       </c>
       <c r="J23" s="3">
+        <v>134800</v>
+      </c>
+      <c r="K23" s="3">
         <v>55200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>13800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>47400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>32300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>743000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>668000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>778000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>609000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>603000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>372000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>303000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>338000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>373000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>344000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>339000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>270000</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>4500</v>
+        <v>7200</v>
       </c>
       <c r="E24" s="3">
-        <v>9000</v>
+        <v>35100</v>
       </c>
       <c r="F24" s="3">
-        <v>4600</v>
+        <v>8900</v>
       </c>
       <c r="G24" s="3">
-        <v>9400</v>
+        <v>36200</v>
       </c>
       <c r="H24" s="3">
-        <v>3300</v>
+        <v>73100</v>
       </c>
       <c r="I24" s="3">
-        <v>1300</v>
+        <v>25500</v>
       </c>
       <c r="J24" s="3">
+        <v>10400</v>
+      </c>
+      <c r="K24" s="3">
         <v>-22200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>188000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>169000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>174000</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>155000</v>
       </c>
       <c r="R24" s="3">
         <v>155000</v>
       </c>
       <c r="S24" s="3">
+        <v>155000</v>
+      </c>
+      <c r="T24" s="3">
         <v>101000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>74000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>127000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>142000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>130000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>123000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>85000</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>58400</v>
+        <v>105700</v>
       </c>
       <c r="E26" s="3">
-        <v>102700</v>
+        <v>455300</v>
       </c>
       <c r="F26" s="3">
-        <v>75900</v>
+        <v>102300</v>
       </c>
       <c r="G26" s="3">
-        <v>80700</v>
+        <v>592200</v>
       </c>
       <c r="H26" s="3">
-        <v>52600</v>
+        <v>629700</v>
       </c>
       <c r="I26" s="3">
-        <v>15900</v>
+        <v>410600</v>
       </c>
       <c r="J26" s="3">
+        <v>124400</v>
+      </c>
+      <c r="K26" s="3">
         <v>77400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>11400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>39200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>28100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>555000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>499000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>604000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>454000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>448000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>271000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>229000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>211000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>231000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>214000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>216000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>47200</v>
+        <v>96600</v>
       </c>
       <c r="E27" s="3">
-        <v>95100</v>
+        <v>368400</v>
       </c>
       <c r="F27" s="3">
-        <v>67900</v>
+        <v>94700</v>
       </c>
       <c r="G27" s="3">
-        <v>72700</v>
+        <v>529400</v>
       </c>
       <c r="H27" s="3">
-        <v>48600</v>
+        <v>567000</v>
       </c>
       <c r="I27" s="3">
-        <v>11900</v>
+        <v>379200</v>
       </c>
       <c r="J27" s="3">
+        <v>93100</v>
+      </c>
+      <c r="K27" s="3">
         <v>75300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>11400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>39200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>28100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>555000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>499000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>604000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>454000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>448000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>271000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>229000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>211000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>231000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>214000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>216000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2153,8 +2214,8 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>5</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>5</v>
@@ -2162,21 +2223,21 @@
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>3000</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>68000</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,65 +2398,68 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-9400</v>
+        <v>-3800</v>
       </c>
       <c r="E32" s="3">
-        <v>-51900</v>
+        <v>-73400</v>
       </c>
       <c r="F32" s="3">
-        <v>-50500</v>
+        <v>-51700</v>
       </c>
       <c r="G32" s="3">
-        <v>-35200</v>
+        <v>-394300</v>
       </c>
       <c r="H32" s="3">
-        <v>-41000</v>
+        <v>-274800</v>
       </c>
       <c r="I32" s="3">
-        <v>-13500</v>
+        <v>-319500</v>
       </c>
       <c r="J32" s="3">
+        <v>-105400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-4500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-36500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-14800</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2000</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>13000</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -2402,79 +2472,85 @@
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>47200</v>
+        <v>96600</v>
       </c>
       <c r="E33" s="3">
-        <v>95100</v>
+        <v>368400</v>
       </c>
       <c r="F33" s="3">
-        <v>67900</v>
+        <v>94700</v>
       </c>
       <c r="G33" s="3">
-        <v>72700</v>
+        <v>529400</v>
       </c>
       <c r="H33" s="3">
-        <v>48600</v>
+        <v>567000</v>
       </c>
       <c r="I33" s="3">
-        <v>11900</v>
+        <v>379200</v>
       </c>
       <c r="J33" s="3">
+        <v>93100</v>
+      </c>
+      <c r="K33" s="3">
         <v>75300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>11400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>39200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>28100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>555000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>499000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>604000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>454000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>451000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>271000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>297000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>211000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>231000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>214000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>216000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>47200</v>
+        <v>96600</v>
       </c>
       <c r="E35" s="3">
-        <v>95100</v>
+        <v>368400</v>
       </c>
       <c r="F35" s="3">
-        <v>67900</v>
+        <v>94700</v>
       </c>
       <c r="G35" s="3">
-        <v>72700</v>
+        <v>529400</v>
       </c>
       <c r="H35" s="3">
-        <v>48600</v>
+        <v>567000</v>
       </c>
       <c r="I35" s="3">
-        <v>11900</v>
+        <v>379200</v>
       </c>
       <c r="J35" s="3">
+        <v>93100</v>
+      </c>
+      <c r="K35" s="3">
         <v>75300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>11400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>39200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>28100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>555000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>499000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>604000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>454000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>451000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>271000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>297000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>211000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>231000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>214000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>216000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44742</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44377</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44104</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43830</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43738</v>
-      </c>
-      <c r="M38" s="2">
-        <v>43646</v>
       </c>
       <c r="N38" s="2">
         <v>43646</v>
       </c>
       <c r="O38" s="2">
+        <v>43646</v>
+      </c>
+      <c r="P38" s="2">
         <v>43555</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43465</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43373</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43281</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43190</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43100</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43008</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>42916</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>42825</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>42735</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,79 +2831,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>162100</v>
+      </c>
+      <c r="E41" s="3">
         <v>139500</v>
       </c>
-      <c r="E41" s="3">
-        <v>30500</v>
-      </c>
       <c r="F41" s="3">
-        <v>84900</v>
+        <v>237700</v>
       </c>
       <c r="G41" s="3">
-        <v>75200</v>
+        <v>662300</v>
       </c>
       <c r="H41" s="3">
-        <v>83500</v>
+        <v>586400</v>
       </c>
       <c r="I41" s="3">
-        <v>83000</v>
+        <v>651300</v>
       </c>
       <c r="J41" s="3">
+        <v>647800</v>
+      </c>
+      <c r="K41" s="3">
         <v>147900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>128900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>122000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>112500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2953000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2674000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5117000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2690000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1343000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1373000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1644000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1472000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2880000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2231000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1662000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1855000</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2833,27 +2923,27 @@
       <c r="G42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H42" s="3">
-        <v>8000</v>
+      <c r="H42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I42" s="3">
-        <v>137200</v>
+        <v>62500</v>
       </c>
       <c r="J42" s="3">
+        <v>1069900</v>
+      </c>
+      <c r="K42" s="3">
         <v>129500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>200400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>223100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>246000</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
@@ -2887,79 +2977,85 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>311500</v>
+        <v>546800</v>
       </c>
       <c r="E43" s="3">
-        <v>661300</v>
+        <v>311600</v>
       </c>
       <c r="F43" s="3">
-        <v>286100</v>
+        <v>5159000</v>
       </c>
       <c r="G43" s="3">
-        <v>900800</v>
+        <v>2231500</v>
       </c>
       <c r="H43" s="3">
-        <v>840400</v>
+        <v>7027000</v>
       </c>
       <c r="I43" s="3">
-        <v>960900</v>
+        <v>6555700</v>
       </c>
       <c r="J43" s="3">
+        <v>7495600</v>
+      </c>
+      <c r="K43" s="3">
         <v>894200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>569500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>446400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>670500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>23014000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>22790000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>21312000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>24445000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>24345000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>22709000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>20287000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>18796000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>15020000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>13393000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>13277000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>13397000</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3029,115 +3125,121 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>309600</v>
+        <v>399000</v>
       </c>
       <c r="E45" s="3">
-        <v>228000</v>
+        <v>309700</v>
       </c>
       <c r="F45" s="3">
-        <v>127100</v>
+        <v>1778300</v>
       </c>
       <c r="G45" s="3">
-        <v>130600</v>
+        <v>991800</v>
       </c>
       <c r="H45" s="3">
-        <v>134300</v>
+        <v>1018700</v>
       </c>
       <c r="I45" s="3">
-        <v>130900</v>
+        <v>1047700</v>
       </c>
       <c r="J45" s="3">
+        <v>1020900</v>
+      </c>
+      <c r="K45" s="3">
         <v>121300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>153000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>109800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>31900</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3">
         <v>4609000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6863000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10136000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>10446000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7328000</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
       <c r="X45" s="3">
         <v>0</v>
       </c>
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>760600</v>
+        <v>1107800</v>
       </c>
       <c r="E46" s="3">
-        <v>919800</v>
+        <v>760900</v>
       </c>
       <c r="F46" s="3">
-        <v>498100</v>
+        <v>7175000</v>
       </c>
       <c r="G46" s="3">
-        <v>1106600</v>
+        <v>3885600</v>
       </c>
       <c r="H46" s="3">
-        <v>1066200</v>
+        <v>8632100</v>
       </c>
       <c r="I46" s="3">
-        <v>1311900</v>
+        <v>8317200</v>
       </c>
       <c r="J46" s="3">
+        <v>10234300</v>
+      </c>
+      <c r="K46" s="3">
         <v>1292900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1051700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>901300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1060900</v>
       </c>
-      <c r="N46" s="3">
-        <v>0</v>
-      </c>
       <c r="O46" s="3">
         <v>0</v>
       </c>
@@ -3171,28 +3273,31 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E47" s="3">
-        <v>38500</v>
+      <c r="D47" s="3">
+        <v>99600</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F47" s="3">
-        <v>27100</v>
+        <v>300200</v>
       </c>
       <c r="G47" s="3">
-        <v>116700</v>
+        <v>211300</v>
       </c>
       <c r="H47" s="3">
-        <v>112600</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
+        <v>910100</v>
+      </c>
+      <c r="I47" s="3">
+        <v>878500</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>5</v>
@@ -3206,64 +3311,67 @@
       <c r="M47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O47" s="3">
         <v>1447000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1053000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>993000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>640000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>682000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>901000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>692000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1249000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1154000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>9831000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>10187000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>9817000</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
+        <v>242700</v>
       </c>
       <c r="E48" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="G48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J48" s="3">
         <v>0</v>
@@ -3278,66 +3386,69 @@
         <v>0</v>
       </c>
       <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3">
         <v>833000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>812000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>797000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>792000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>778000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>801000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>780000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>752000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>592000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>555000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>531000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>526000</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>92700</v>
+      </c>
+      <c r="E49" s="3">
         <v>104500</v>
       </c>
-      <c r="E49" s="3">
-        <v>102100</v>
-      </c>
       <c r="F49" s="3">
-        <v>1900</v>
+        <v>796400</v>
       </c>
       <c r="G49" s="3">
-        <v>1900</v>
+        <v>15200</v>
       </c>
       <c r="H49" s="3">
-        <v>1900</v>
+        <v>15200</v>
       </c>
       <c r="I49" s="3">
-        <v>1900</v>
+        <v>15200</v>
       </c>
       <c r="J49" s="3">
-        <v>1900</v>
+        <v>15200</v>
       </c>
       <c r="K49" s="3">
         <v>1900</v>
@@ -3349,43 +3460,46 @@
         <v>1900</v>
       </c>
       <c r="N49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O49" s="3">
         <v>5463000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5494000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5525000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5556000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5561000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5597000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5629000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5683000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2985000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3004000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3023000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3042000</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,28 +3643,31 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>144100</v>
+      </c>
+      <c r="E52" s="3">
         <v>195300</v>
       </c>
-      <c r="E52" s="3">
-        <v>184200</v>
-      </c>
       <c r="F52" s="3">
-        <v>330100</v>
+        <v>1436700</v>
       </c>
       <c r="G52" s="3">
-        <v>195300</v>
+        <v>2574700</v>
       </c>
       <c r="H52" s="3">
-        <v>168600</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
+        <v>1523800</v>
+      </c>
+      <c r="I52" s="3">
+        <v>1315300</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
@@ -3561,20 +3681,20 @@
       <c r="M52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O52" s="3">
         <v>7124000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5580000</v>
-      </c>
-      <c r="P52" s="3">
-        <v>3185000</v>
       </c>
       <c r="Q52" s="3">
         <v>3185000</v>
       </c>
       <c r="R52" s="3">
-        <v>0</v>
+        <v>3185000</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -3597,8 +3717,11 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3791,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1060300</v>
+        <v>1687000</v>
       </c>
       <c r="E54" s="3">
-        <v>1245000</v>
+        <v>1060700</v>
       </c>
       <c r="F54" s="3">
-        <v>857200</v>
+        <v>9712100</v>
       </c>
       <c r="G54" s="3">
-        <v>1420500</v>
+        <v>6686800</v>
       </c>
       <c r="H54" s="3">
-        <v>1349400</v>
+        <v>11081200</v>
       </c>
       <c r="I54" s="3">
-        <v>1313900</v>
+        <v>10526300</v>
       </c>
       <c r="J54" s="3">
+        <v>10249500</v>
+      </c>
+      <c r="K54" s="3">
         <v>1294800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1053700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>903200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1062800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>41119000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>38679000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>37191000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>37520000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>37511000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>38410000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>39412000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>38627000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>30110000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>29165000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>28834000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>28818000</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,115 +3923,119 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>27400</v>
+        <v>43500</v>
       </c>
       <c r="E57" s="3">
-        <v>60000</v>
+        <v>27500</v>
       </c>
       <c r="F57" s="3">
-        <v>31700</v>
+        <v>468200</v>
       </c>
       <c r="G57" s="3">
-        <v>41100</v>
+        <v>247200</v>
       </c>
       <c r="H57" s="3">
-        <v>36300</v>
+        <v>320900</v>
       </c>
       <c r="I57" s="3">
-        <v>54100</v>
+        <v>283000</v>
       </c>
       <c r="J57" s="3">
+        <v>421900</v>
+      </c>
+      <c r="K57" s="3">
         <v>82300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>71100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>62400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>460100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>28833000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>26621000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>25139000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>26805000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>26859000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>27889000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>29119000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>28535000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>21821000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>21806000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>21582000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>21669000</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E58" s="3">
         <v>20100</v>
       </c>
-      <c r="E58" s="3">
-        <v>21000</v>
-      </c>
       <c r="F58" s="3">
-        <v>49800</v>
+        <v>163900</v>
       </c>
       <c r="G58" s="3">
-        <v>29800</v>
+        <v>388900</v>
       </c>
       <c r="H58" s="3">
-        <v>29800</v>
+        <v>232500</v>
       </c>
       <c r="I58" s="3">
-        <v>29800</v>
+        <v>232300</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>232300</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>40500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>41000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>41100</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -3909,23 +4043,23 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>96000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>97000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>318000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>147000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>97000</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>5</v>
       </c>
@@ -3935,44 +4069,47 @@
       <c r="Y58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>67100</v>
+      </c>
+      <c r="E59" s="3">
         <v>7000</v>
       </c>
-      <c r="E59" s="3">
-        <v>20500</v>
-      </c>
       <c r="F59" s="3">
-        <v>17400</v>
+        <v>159700</v>
       </c>
       <c r="G59" s="3">
-        <v>12800</v>
+        <v>136100</v>
       </c>
       <c r="H59" s="3">
-        <v>21900</v>
+        <v>99900</v>
       </c>
       <c r="I59" s="3">
-        <v>12500</v>
+        <v>170600</v>
       </c>
       <c r="J59" s="3">
+        <v>97800</v>
+      </c>
+      <c r="K59" s="3">
         <v>11200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>26300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7500</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
@@ -3985,8 +4122,8 @@
       <c r="R59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S59" s="3">
-        <v>0</v>
+      <c r="S59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T59" s="3">
         <v>0</v>
@@ -4006,44 +4143,47 @@
       <c r="Y59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>176700</v>
+      </c>
+      <c r="E60" s="3">
         <v>54500</v>
       </c>
-      <c r="E60" s="3">
-        <v>101500</v>
-      </c>
       <c r="F60" s="3">
-        <v>99000</v>
+        <v>791900</v>
       </c>
       <c r="G60" s="3">
-        <v>83800</v>
+        <v>772200</v>
       </c>
       <c r="H60" s="3">
-        <v>87900</v>
+        <v>653300</v>
       </c>
       <c r="I60" s="3">
-        <v>96400</v>
+        <v>685900</v>
       </c>
       <c r="J60" s="3">
+        <v>752000</v>
+      </c>
+      <c r="K60" s="3">
         <v>93500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>137900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>113100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>508800</v>
       </c>
-      <c r="N60" s="3">
-        <v>0</v>
-      </c>
       <c r="O60" s="3">
         <v>0</v>
       </c>
@@ -4077,150 +4217,159 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E61" s="3">
         <v>500</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
-        <v>14400</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>13800</v>
+        <v>112000</v>
       </c>
       <c r="H61" s="3">
-        <v>13200</v>
+        <v>107400</v>
       </c>
       <c r="I61" s="3">
-        <v>13000</v>
+        <v>103300</v>
       </c>
       <c r="J61" s="3">
+        <v>101400</v>
+      </c>
+      <c r="K61" s="3">
         <v>12800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12200</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>3574000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3520000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3484000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2439000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2456000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2477000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2531000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2555000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2561000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1765000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1769000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1817000</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E62" s="3">
         <v>3300</v>
       </c>
-      <c r="E62" s="3">
-        <v>9800</v>
-      </c>
       <c r="F62" s="3">
-        <v>1800</v>
+        <v>76700</v>
       </c>
       <c r="G62" s="3">
-        <v>1800</v>
+        <v>13800</v>
       </c>
       <c r="H62" s="3">
-        <v>1700</v>
+        <v>13700</v>
       </c>
       <c r="I62" s="3">
+        <v>13000</v>
+      </c>
+      <c r="J62" s="3">
+        <v>20700</v>
+      </c>
+      <c r="K62" s="3">
         <v>2700</v>
       </c>
-      <c r="J62" s="3">
-        <v>2700</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>33600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>31000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>25000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>219000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>215000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>211000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>177000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>163000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>131000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>182000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>193000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>268000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>269000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>284000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>281000</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4587,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>343600</v>
+      </c>
+      <c r="E66" s="3">
         <v>90000</v>
       </c>
-      <c r="E66" s="3">
-        <v>124800</v>
-      </c>
       <c r="F66" s="3">
-        <v>117100</v>
+        <v>973700</v>
       </c>
       <c r="G66" s="3">
-        <v>101300</v>
+        <v>913500</v>
       </c>
       <c r="H66" s="3">
-        <v>102800</v>
+        <v>789900</v>
       </c>
       <c r="I66" s="3">
-        <v>112000</v>
+        <v>802100</v>
       </c>
       <c r="J66" s="3">
+        <v>874000</v>
+      </c>
+      <c r="K66" s="3">
         <v>108900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>183700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>144000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>533700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>32626000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>30356000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>28834000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>29517000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>29575000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>30815000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>31979000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>31380000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>24650000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>23840000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>23635000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>23767000</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +4985,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1704200</v>
+        <v>1804500</v>
       </c>
       <c r="E72" s="3">
-        <v>1533900</v>
+        <v>1701800</v>
       </c>
       <c r="F72" s="3">
-        <v>1153800</v>
+        <v>11965900</v>
       </c>
       <c r="G72" s="3">
-        <v>1083900</v>
+        <v>9000700</v>
       </c>
       <c r="H72" s="3">
-        <v>1011200</v>
+        <v>8455300</v>
       </c>
       <c r="I72" s="3">
-        <v>962600</v>
+        <v>7888300</v>
       </c>
       <c r="J72" s="3">
+        <v>7509200</v>
+      </c>
+      <c r="K72" s="3">
         <v>950700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>869900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>759100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>529100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8194000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7805000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7475000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7011000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6673000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6341000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6189000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6011000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5895000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5759000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5640000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5518000</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5281,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>970300</v>
+        <v>1343300</v>
       </c>
       <c r="E76" s="3">
-        <v>1120200</v>
+        <v>970700</v>
       </c>
       <c r="F76" s="3">
-        <v>740100</v>
+        <v>8738400</v>
       </c>
       <c r="G76" s="3">
-        <v>1319200</v>
+        <v>5773400</v>
       </c>
       <c r="H76" s="3">
-        <v>1246500</v>
+        <v>10291300</v>
       </c>
       <c r="I76" s="3">
-        <v>1201800</v>
+        <v>9724200</v>
       </c>
       <c r="J76" s="3">
+        <v>9375400</v>
+      </c>
+      <c r="K76" s="3">
         <v>1185900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>870000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>759200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>529100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8493000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8323000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8357000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8003000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7936000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7595000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7433000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7247000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5460000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5325000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5199000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5051000</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44742</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44377</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44104</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43830</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43738</v>
-      </c>
-      <c r="M80" s="2">
-        <v>43646</v>
       </c>
       <c r="N80" s="2">
         <v>43646</v>
       </c>
       <c r="O80" s="2">
+        <v>43646</v>
+      </c>
+      <c r="P80" s="2">
         <v>43555</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43465</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43373</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43281</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43190</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43100</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43008</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>42916</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>42825</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>42735</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>47200</v>
+        <v>96600</v>
       </c>
       <c r="E81" s="3">
-        <v>95100</v>
+        <v>368400</v>
       </c>
       <c r="F81" s="3">
-        <v>67900</v>
+        <v>94700</v>
       </c>
       <c r="G81" s="3">
-        <v>72700</v>
+        <v>529400</v>
       </c>
       <c r="H81" s="3">
-        <v>48600</v>
+        <v>567000</v>
       </c>
       <c r="I81" s="3">
-        <v>11900</v>
+        <v>379200</v>
       </c>
       <c r="J81" s="3">
+        <v>93100</v>
+      </c>
+      <c r="K81" s="3">
         <v>75300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>11400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>39200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>28100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>555000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>499000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>604000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>454000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>451000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>271000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>297000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>211000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>231000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>214000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>216000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5612,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5450,43 +5649,46 @@
         <v>0</v>
       </c>
       <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
         <v>69000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>67000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>66000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>70000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>69000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>72000</v>
       </c>
       <c r="T83" s="3">
         <v>72000</v>
       </c>
       <c r="U83" s="3">
+        <v>72000</v>
+      </c>
+      <c r="V83" s="3">
         <v>50000</v>
-      </c>
-      <c r="V83" s="3">
-        <v>44000</v>
       </c>
       <c r="W83" s="3">
         <v>44000</v>
       </c>
       <c r="X83" s="3">
+        <v>44000</v>
+      </c>
+      <c r="Y83" s="3">
         <v>43000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>45000</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,8 +6054,11 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5876,43 +6093,46 @@
         <v>0</v>
       </c>
       <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
         <v>2438000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>573000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2762000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1821000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>349000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>124000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-386000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>23000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>27000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>718000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-81000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>436000</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,8 +6158,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5974,43 +6195,46 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-59000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-48000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-44000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-63000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-47000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-56000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-63000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-56000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-62000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-58000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-27000</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,8 +6378,11 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6187,43 +6417,46 @@
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-195000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-48000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-426000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-66000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-35000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-440000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>633000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1406000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-62000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-50000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-29000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-384000</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6482,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6285,19 +6519,19 @@
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-166000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-169000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-168000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-120000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-119000</v>
       </c>
       <c r="S96" s="3">
         <v>-119000</v>
@@ -6306,10 +6540,10 @@
         <v>-119000</v>
       </c>
       <c r="U96" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-94000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-95000</v>
       </c>
       <c r="W96" s="3">
         <v>-95000</v>
@@ -6318,10 +6552,13 @@
         <v>-95000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,8 +6776,11 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6569,43 +6815,46 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-409000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-552000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>594000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-408000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-344000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>45000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-75000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-37000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>685000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-97000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-74000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-114000</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6675,8 +6924,11 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6711,39 +6963,42 @@
         <v>0</v>
       </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>1834000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-27000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2930000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1347000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-30000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-271000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>172000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1408000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>649000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>569000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-193000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-62000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMTD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMTD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
   <si>
     <t>AMTD</t>
   </si>
@@ -656,197 +656,204 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44104</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43830</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43738</v>
-      </c>
-      <c r="N7" s="2">
-        <v>43646</v>
       </c>
       <c r="O7" s="2">
         <v>43646</v>
       </c>
       <c r="P7" s="2">
+        <v>43646</v>
+      </c>
+      <c r="Q7" s="2">
         <v>43555</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43465</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43373</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43281</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43190</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43008</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>42916</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>42825</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>50600</v>
+      </c>
+      <c r="E8" s="3">
         <v>135500</v>
       </c>
-      <c r="E8" s="3">
-        <v>459800</v>
-      </c>
       <c r="F8" s="3">
+        <v>58700</v>
+      </c>
+      <c r="G8" s="3">
         <v>75200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>335000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>519300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>155300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>83900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>69100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>25000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1491000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1451000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1516000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1398000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1382000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1415000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1257000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>983000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>931000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>904000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>859000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>830000</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
+      <c r="D9" s="3">
+        <v>14300</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>5</v>
@@ -878,18 +885,18 @@
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3">
         <v>59000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>53000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>49000</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>5</v>
       </c>
@@ -914,13 +921,16 @@
       <c r="Z9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>36300</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>5</v>
@@ -952,18 +962,18 @@
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3">
         <v>1432000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1398000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1467000</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>5</v>
       </c>
@@ -988,8 +998,11 @@
       <c r="Z10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,8 +1029,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1090,8 +1104,11 @@
       <c r="Z12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,19 +1181,22 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3">
-        <v>3900</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
+        <v>500</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
@@ -1184,12 +1204,12 @@
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>17100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1202,44 +1222,47 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>-60000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
         <v>1000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>1000</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1277,43 +1300,46 @@
         <v>0</v>
       </c>
       <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
         <v>69000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>67000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>66000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>70000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>69000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>72000</v>
       </c>
       <c r="U15" s="3">
         <v>72000</v>
       </c>
       <c r="V15" s="3">
+        <v>72000</v>
+      </c>
+      <c r="W15" s="3">
         <v>50000</v>
-      </c>
-      <c r="W15" s="3">
-        <v>44000</v>
       </c>
       <c r="X15" s="3">
         <v>44000</v>
       </c>
       <c r="Y15" s="3">
+        <v>44000</v>
+      </c>
+      <c r="Z15" s="3">
         <v>43000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>45000</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1363,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>-22900</v>
+      </c>
+      <c r="E17" s="3">
         <v>22800</v>
       </c>
-      <c r="E17" s="3">
-        <v>38600</v>
-      </c>
       <c r="F17" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G17" s="3">
         <v>15300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>94500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>84900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>34700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>51500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7300</v>
-      </c>
-      <c r="M17" s="3">
-        <v>6900</v>
       </c>
       <c r="N17" s="3">
         <v>6900</v>
       </c>
       <c r="O17" s="3">
+        <v>6900</v>
+      </c>
+      <c r="P17" s="3">
         <v>711000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>746000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>720000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>764000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>751000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1019000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>921000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>622000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>538000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>546000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>506000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>546000</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>73500</v>
+      </c>
+      <c r="E18" s="3">
         <v>112700</v>
       </c>
-      <c r="E18" s="3">
-        <v>421200</v>
-      </c>
       <c r="F18" s="3">
+        <v>53800</v>
+      </c>
+      <c r="G18" s="3">
         <v>59900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>240500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>434400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>120600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>32400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>52600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>18200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>780000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>705000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>796000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>634000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>631000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>396000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>336000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>361000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>393000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>358000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>353000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>284000</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,68 +1546,69 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="E20" s="3">
         <v>3800</v>
       </c>
-      <c r="E20" s="3">
-        <v>73400</v>
-      </c>
       <c r="F20" s="3">
+        <v>9400</v>
+      </c>
+      <c r="G20" s="3">
         <v>51700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>394300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>274800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>319500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>105400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>36500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>14800</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>14000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2000</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-13000</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1587,8 +1621,11 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1616,118 +1653,121 @@
       <c r="K21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M21" s="3">
         <v>15300</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>849000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>772000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>876000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>706000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>700000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>468000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>395000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>411000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>437000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>402000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>396000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>329000</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E22" s="3">
         <v>3600</v>
       </c>
-      <c r="E22" s="3">
-        <v>4200</v>
-      </c>
       <c r="F22" s="3">
+        <v>500</v>
+      </c>
+      <c r="G22" s="3">
         <v>300</v>
-      </c>
-      <c r="G22" s="3">
-        <v>6400</v>
       </c>
       <c r="H22" s="3">
         <v>6400</v>
       </c>
       <c r="I22" s="3">
+        <v>6400</v>
+      </c>
+      <c r="J22" s="3">
         <v>3900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1500</v>
-      </c>
-      <c r="M22" s="3">
-        <v>700</v>
       </c>
       <c r="N22" s="3">
         <v>700</v>
       </c>
       <c r="O22" s="3">
-        <v>37000</v>
+        <v>700</v>
       </c>
       <c r="P22" s="3">
         <v>37000</v>
       </c>
       <c r="Q22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="R22" s="3">
         <v>32000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>27000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>28000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>24000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>20000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>23000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>20000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>14000</v>
       </c>
       <c r="Y22" s="3">
         <v>14000</v>
@@ -1735,156 +1775,165 @@
       <c r="Z22" s="3">
         <v>14000</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E23" s="3">
         <v>113000</v>
       </c>
-      <c r="E23" s="3">
-        <v>490400</v>
-      </c>
       <c r="F23" s="3">
+        <v>62600</v>
+      </c>
+      <c r="G23" s="3">
         <v>111300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>628400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>702800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>436100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>134800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>55200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>13800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>47400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>32300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>743000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>668000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>778000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>609000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>603000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>372000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>303000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>338000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>373000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>344000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>339000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>270000</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E24" s="3">
         <v>7200</v>
       </c>
-      <c r="E24" s="3">
-        <v>35100</v>
-      </c>
       <c r="F24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="G24" s="3">
         <v>8900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>36200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>73100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>25500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>10400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-22200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>188000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>169000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>174000</v>
-      </c>
-      <c r="R24" s="3">
-        <v>155000</v>
       </c>
       <c r="S24" s="3">
         <v>155000</v>
       </c>
       <c r="T24" s="3">
+        <v>155000</v>
+      </c>
+      <c r="U24" s="3">
         <v>101000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>74000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>127000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>142000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>130000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>123000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>85000</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2006,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E26" s="3">
         <v>105700</v>
       </c>
-      <c r="E26" s="3">
-        <v>455300</v>
-      </c>
       <c r="F26" s="3">
+        <v>58100</v>
+      </c>
+      <c r="G26" s="3">
         <v>102300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>592200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>629700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>410600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>124400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>77400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>11400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>39200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>28100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>555000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>499000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>604000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>454000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>448000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>271000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>229000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>211000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>231000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>214000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>216000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E27" s="3">
         <v>96600</v>
       </c>
-      <c r="E27" s="3">
-        <v>368400</v>
-      </c>
       <c r="F27" s="3">
+        <v>47000</v>
+      </c>
+      <c r="G27" s="3">
         <v>94700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>529400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>567000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>379200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>93100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>75300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>11400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>39200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>28100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>555000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>499000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>604000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>454000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>448000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>271000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>229000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>211000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>231000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>214000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>216000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2237,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2217,8 +2278,8 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>5</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>5</v>
@@ -2226,21 +2287,21 @@
       <c r="Q29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>3000</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>68000</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2253,8 +2314,11 @@
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2391,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,68 +2468,71 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3800</v>
       </c>
-      <c r="E32" s="3">
-        <v>-73400</v>
-      </c>
       <c r="F32" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="G32" s="3">
         <v>-51700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-394300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-274800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-319500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-105400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-36500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-14800</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-14000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2000</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>13000</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -2475,82 +2545,88 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E33" s="3">
         <v>96600</v>
       </c>
-      <c r="E33" s="3">
-        <v>368400</v>
-      </c>
       <c r="F33" s="3">
+        <v>47000</v>
+      </c>
+      <c r="G33" s="3">
         <v>94700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>529400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>567000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>379200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>93100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>75300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>11400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>39200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>28100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>555000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>499000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>604000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>454000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>451000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>271000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>297000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>211000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>231000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>214000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>216000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2699,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E35" s="3">
         <v>96600</v>
       </c>
-      <c r="E35" s="3">
-        <v>368400</v>
-      </c>
       <c r="F35" s="3">
+        <v>47000</v>
+      </c>
+      <c r="G35" s="3">
         <v>94700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>529400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>567000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>379200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>93100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>75300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>11400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>39200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>28100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>555000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>499000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>604000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>454000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>451000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>271000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>297000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>211000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>231000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>214000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>216000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44104</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43830</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43738</v>
-      </c>
-      <c r="N38" s="2">
-        <v>43646</v>
       </c>
       <c r="O38" s="2">
         <v>43646</v>
       </c>
       <c r="P38" s="2">
+        <v>43646</v>
+      </c>
+      <c r="Q38" s="2">
         <v>43555</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43465</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43373</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43281</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43190</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43008</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>42916</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>42825</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2889,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,82 +2918,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>121300</v>
+      </c>
+      <c r="E41" s="3">
         <v>162100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>139500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>237700</v>
       </c>
-      <c r="G41" s="3">
-        <v>662300</v>
-      </c>
       <c r="H41" s="3">
+        <v>84900</v>
+      </c>
+      <c r="I41" s="3">
         <v>586400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>651300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>647800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>147900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>128900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>122000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>112500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2953000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2674000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5117000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2690000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1343000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1373000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1644000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1472000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2880000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2231000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1662000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1855000</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2926,27 +3016,27 @@
       <c r="H42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I42" s="3">
+      <c r="I42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J42" s="3">
         <v>62500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1069900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>129500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>200400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>223100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>246000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -2980,82 +3070,88 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1064900</v>
+      </c>
+      <c r="E43" s="3">
         <v>546800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>311600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5159000</v>
       </c>
-      <c r="G43" s="3">
-        <v>2231500</v>
-      </c>
       <c r="H43" s="3">
+        <v>286200</v>
+      </c>
+      <c r="I43" s="3">
         <v>7027000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6555700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7495600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>894200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>569500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>446400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>670500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>23014000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>22790000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>21312000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>24445000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>24345000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>22709000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>20287000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>18796000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>15020000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>13393000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>13277000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>13397000</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3128,121 +3224,127 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E45" s="3">
         <v>399000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>309700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1778300</v>
       </c>
-      <c r="G45" s="3">
-        <v>991800</v>
-      </c>
       <c r="H45" s="3">
+        <v>127200</v>
+      </c>
+      <c r="I45" s="3">
         <v>1018700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1047700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1020900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>121300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>153000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>109800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>31900</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R45" s="3">
-        <v>0</v>
+      <c r="R45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3">
         <v>4609000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6863000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>10136000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10446000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7328000</v>
       </c>
-      <c r="X45" s="3">
-        <v>0</v>
-      </c>
       <c r="Y45" s="3">
         <v>0</v>
       </c>
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1202700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1107800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>760900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7175000</v>
       </c>
-      <c r="G46" s="3">
-        <v>3885600</v>
-      </c>
       <c r="H46" s="3">
+        <v>498400</v>
+      </c>
+      <c r="I46" s="3">
         <v>8632100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8317200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10234300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1292900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1051700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>901300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1060900</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -3276,32 +3378,35 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E47" s="3">
         <v>99600</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3">
         <v>300200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>211300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>910100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>878500</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3314,67 +3419,70 @@
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P47" s="3">
         <v>1447000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1053000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>993000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>640000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>682000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>901000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>692000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1249000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1154000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>9831000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>10187000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>9817000</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>70100</v>
+      </c>
+      <c r="E48" s="3">
         <v>242700</v>
       </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
       <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
         <v>3800</v>
       </c>
-      <c r="G48" s="3">
-        <v>100</v>
-      </c>
       <c r="H48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3">
         <v>100</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -3389,60 +3497,63 @@
         <v>0</v>
       </c>
       <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3">
         <v>833000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>812000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>797000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>792000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>778000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>801000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>780000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>752000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>592000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>555000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>531000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>526000</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>118400</v>
+      </c>
+      <c r="E49" s="3">
         <v>92700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>104500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>796400</v>
       </c>
-      <c r="G49" s="3">
-        <v>15200</v>
-      </c>
       <c r="H49" s="3">
-        <v>15200</v>
+        <v>1900</v>
       </c>
       <c r="I49" s="3">
         <v>15200</v>
@@ -3451,7 +3562,7 @@
         <v>15200</v>
       </c>
       <c r="K49" s="3">
-        <v>1900</v>
+        <v>15200</v>
       </c>
       <c r="L49" s="3">
         <v>1900</v>
@@ -3463,43 +3574,46 @@
         <v>1900</v>
       </c>
       <c r="O49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="P49" s="3">
         <v>5463000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5494000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5525000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5556000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5561000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5597000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5629000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5683000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2985000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3004000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3023000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3042000</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3686,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,32 +3763,35 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>79600</v>
+      </c>
+      <c r="E52" s="3">
         <v>144100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>195300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1436700</v>
       </c>
-      <c r="G52" s="3">
-        <v>2574700</v>
-      </c>
       <c r="H52" s="3">
+        <v>357400</v>
+      </c>
+      <c r="I52" s="3">
         <v>1523800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1315300</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3684,20 +3804,20 @@
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P52" s="3">
         <v>7124000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5580000</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>3185000</v>
       </c>
       <c r="R52" s="3">
         <v>3185000</v>
       </c>
       <c r="S52" s="3">
-        <v>0</v>
+        <v>3185000</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
@@ -3720,8 +3840,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +3917,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1486600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1687000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1060700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9712100</v>
       </c>
-      <c r="G54" s="3">
-        <v>6686800</v>
-      </c>
       <c r="H54" s="3">
+        <v>857700</v>
+      </c>
+      <c r="I54" s="3">
         <v>11081200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10526300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10249500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1294800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1053700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>903200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1062800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>41119000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>38679000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>37191000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>37520000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>37511000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>38410000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>39412000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>38627000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>30110000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>29165000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>28834000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>28818000</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4025,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,121 +4054,125 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E57" s="3">
         <v>43500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>27500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>468200</v>
       </c>
-      <c r="G57" s="3">
-        <v>247200</v>
-      </c>
       <c r="H57" s="3">
+        <v>31700</v>
+      </c>
+      <c r="I57" s="3">
         <v>320900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>283000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>421900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>82300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>71100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>62400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>460100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>28833000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>26621000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>25139000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>26805000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>26859000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>27889000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>29119000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>28535000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>21821000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>21806000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>21582000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>21669000</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>65800</v>
+      </c>
+      <c r="E58" s="3">
         <v>66000</v>
       </c>
-      <c r="E58" s="3">
-        <v>20100</v>
-      </c>
       <c r="F58" s="3">
+        <v>177000</v>
+      </c>
+      <c r="G58" s="3">
         <v>163900</v>
       </c>
-      <c r="G58" s="3">
-        <v>388900</v>
-      </c>
       <c r="H58" s="3">
+        <v>49900</v>
+      </c>
+      <c r="I58" s="3">
         <v>232500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>232300</v>
       </c>
       <c r="J58" s="3">
         <v>232300</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>232300</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>40500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>41000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>41100</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -4046,23 +4180,23 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>96000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>97000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>318000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>147000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>97000</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>5</v>
       </c>
@@ -4072,47 +4206,50 @@
       <c r="Z58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E59" s="3">
         <v>67100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>159700</v>
       </c>
-      <c r="G59" s="3">
-        <v>136100</v>
-      </c>
       <c r="H59" s="3">
+        <v>17500</v>
+      </c>
+      <c r="I59" s="3">
         <v>99900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>170600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>97800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>26300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7500</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4125,8 +4262,8 @@
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T59" s="3">
-        <v>0</v>
+      <c r="T59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U59" s="3">
         <v>0</v>
@@ -4146,47 +4283,50 @@
       <c r="Z59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>157100</v>
+      </c>
+      <c r="E60" s="3">
         <v>176700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>54500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>791900</v>
       </c>
-      <c r="G60" s="3">
-        <v>772200</v>
-      </c>
       <c r="H60" s="3">
+        <v>99100</v>
+      </c>
+      <c r="I60" s="3">
         <v>653300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>685900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>752000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>93500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>137900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>113100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>508800</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -4220,8 +4360,11 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4229,147 +4372,153 @@
         <v>30400</v>
       </c>
       <c r="E61" s="3">
+        <v>30400</v>
+      </c>
+      <c r="F61" s="3">
         <v>500</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
-        <v>112000</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>14400</v>
+      </c>
+      <c r="I61" s="3">
         <v>107400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>103300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>101400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12200</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>3574000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3520000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3484000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2439000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2456000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2477000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2531000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2555000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2561000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1765000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1769000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1817000</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E62" s="3">
         <v>2600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>76700</v>
       </c>
-      <c r="G62" s="3">
-        <v>13800</v>
-      </c>
       <c r="H62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I62" s="3">
         <v>13700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>20700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>33600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>31000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>25000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>219000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>215000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>211000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>177000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>163000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>131000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>182000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>193000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>268000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>269000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>284000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>281000</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4591,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4668,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,82 +4745,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>200100</v>
+      </c>
+      <c r="E66" s="3">
         <v>343600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>90000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>973700</v>
       </c>
-      <c r="G66" s="3">
-        <v>913500</v>
-      </c>
       <c r="H66" s="3">
+        <v>117600</v>
+      </c>
+      <c r="I66" s="3">
         <v>789900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>802100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>874000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>108900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>183700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>144000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>533700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>32626000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>30356000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>28834000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>29517000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>29575000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>30815000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>31979000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>31380000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>24650000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>23840000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>23635000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>23767000</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4853,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4928,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5005,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5082,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,82 +5159,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1784200</v>
+      </c>
+      <c r="E72" s="3">
         <v>1804500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1701800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11965900</v>
       </c>
-      <c r="G72" s="3">
-        <v>9000700</v>
-      </c>
       <c r="H72" s="3">
+        <v>1153100</v>
+      </c>
+      <c r="I72" s="3">
         <v>8455300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7888300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7509200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>950700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>869900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>759100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>529100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8194000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7805000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7475000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7011000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6673000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6341000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6189000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6011000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5895000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5759000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5640000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5518000</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5313,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5390,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5467,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1286500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1343300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>970700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8738400</v>
       </c>
-      <c r="G76" s="3">
-        <v>5773400</v>
-      </c>
       <c r="H76" s="3">
+        <v>740100</v>
+      </c>
+      <c r="I76" s="3">
         <v>10291300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9724200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9375400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1185900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>870000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>759200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>529100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8493000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8323000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8357000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8003000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7936000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7595000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7433000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7247000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5460000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5325000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5199000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5051000</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5621,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44104</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43830</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43738</v>
-      </c>
-      <c r="N80" s="2">
-        <v>43646</v>
       </c>
       <c r="O80" s="2">
         <v>43646</v>
       </c>
       <c r="P80" s="2">
+        <v>43646</v>
+      </c>
+      <c r="Q80" s="2">
         <v>43555</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43465</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43373</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43281</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43190</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43008</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>42916</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>42825</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E81" s="3">
         <v>96600</v>
       </c>
-      <c r="E81" s="3">
-        <v>368400</v>
-      </c>
       <c r="F81" s="3">
+        <v>47000</v>
+      </c>
+      <c r="G81" s="3">
         <v>94700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>529400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>567000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>379200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>93100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>75300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>11400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>39200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>28100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>555000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>499000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>604000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>454000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>451000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>271000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>297000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>211000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>231000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>214000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>216000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,8 +5811,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5652,43 +5851,46 @@
         <v>0</v>
       </c>
       <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
         <v>69000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>67000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>66000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>70000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>69000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>72000</v>
       </c>
       <c r="U83" s="3">
         <v>72000</v>
       </c>
       <c r="V83" s="3">
+        <v>72000</v>
+      </c>
+      <c r="W83" s="3">
         <v>50000</v>
-      </c>
-      <c r="W83" s="3">
-        <v>44000</v>
       </c>
       <c r="X83" s="3">
         <v>44000</v>
       </c>
       <c r="Y83" s="3">
+        <v>44000</v>
+      </c>
+      <c r="Z83" s="3">
         <v>43000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>45000</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5963,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6040,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6117,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6194,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,8 +6271,11 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6096,43 +6313,46 @@
         <v>0</v>
       </c>
       <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
         <v>2438000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>573000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2762000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1821000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>349000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>124000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-386000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>23000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>27000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>718000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-81000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>436000</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,8 +6379,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6198,43 +6419,46 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-59000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-48000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-44000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-63000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-47000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-56000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-63000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-56000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-62000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-58000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-27000</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6531,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,8 +6608,11 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6420,43 +6650,46 @@
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-195000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-48000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-426000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-66000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-35000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-440000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>633000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1406000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-62000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-50000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-29000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-384000</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6716,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6522,19 +6756,19 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-166000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-169000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-168000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-120000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-119000</v>
       </c>
       <c r="T96" s="3">
         <v>-119000</v>
@@ -6543,10 +6777,10 @@
         <v>-119000</v>
       </c>
       <c r="V96" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-94000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-95000</v>
       </c>
       <c r="X96" s="3">
         <v>-95000</v>
@@ -6555,10 +6789,13 @@
         <v>-95000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6868,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6945,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,8 +7022,11 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6818,43 +7064,46 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-409000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-552000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>594000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-408000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-344000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>45000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-75000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-37000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>685000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-97000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-74000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-114000</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6927,8 +7176,11 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6966,39 +7218,42 @@
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>1834000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2930000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1347000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-30000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-271000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>172000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1408000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>649000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>569000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-193000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-62000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMTD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMTD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
   <si>
     <t>AMTD</t>
   </si>
@@ -662,13 +662,12 @@
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -702,22 +701,22 @@
         <v>45291</v>
       </c>
       <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>44834</v>
+      </c>
+      <c r="J7" s="2">
         <v>44742</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44377</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44196</v>
       </c>
       <c r="K7" s="2">
         <v>44104</v>
@@ -775,26 +774,26 @@
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>50600</v>
-      </c>
-      <c r="E8" s="3">
-        <v>135500</v>
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F8" s="3">
-        <v>58700</v>
+        <v>62200</v>
       </c>
       <c r="G8" s="3">
-        <v>75200</v>
+        <v>62200</v>
       </c>
       <c r="H8" s="3">
-        <v>335000</v>
+        <v>28400</v>
       </c>
       <c r="I8" s="3">
-        <v>519300</v>
+        <v>28400</v>
       </c>
       <c r="J8" s="3">
-        <v>155300</v>
+        <v>58600</v>
       </c>
       <c r="K8" s="3">
         <v>83900</v>
@@ -852,8 +851,8 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>14300</v>
+      <c r="D9" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>5</v>
@@ -930,25 +929,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>36300</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+        <v>-800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F10" s="3">
+        <v>62200</v>
+      </c>
+      <c r="G10" s="3">
+        <v>62200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>28400</v>
+      </c>
+      <c r="I10" s="3">
+        <v>28400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>58600</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1035,11 +1034,11 @@
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>5</v>
+      <c r="D12" s="3">
+        <v>400</v>
+      </c>
+      <c r="E12" s="3">
+        <v>400</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>5</v>
@@ -1047,11 +1046,11 @@
       <c r="G12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>5</v>
+      <c r="H12" s="3">
+        <v>400</v>
+      </c>
+      <c r="I12" s="3">
+        <v>400</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>5</v>
@@ -1190,25 +1189,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>5000</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
-        <v>500</v>
+        <v>-35800</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-35800</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
-        <v>17100</v>
+      <c r="H14" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
@@ -1267,7 +1266,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -1370,25 +1369,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>-22900</v>
+        <v>15700</v>
       </c>
       <c r="E17" s="3">
-        <v>22800</v>
+        <v>15700</v>
       </c>
       <c r="F17" s="3">
-        <v>4900</v>
+        <v>11400</v>
       </c>
       <c r="G17" s="3">
-        <v>15300</v>
+        <v>11400</v>
       </c>
       <c r="H17" s="3">
-        <v>94500</v>
+        <v>12100</v>
       </c>
       <c r="I17" s="3">
-        <v>84900</v>
+        <v>12100</v>
       </c>
       <c r="J17" s="3">
-        <v>34700</v>
+        <v>7600</v>
       </c>
       <c r="K17" s="3">
         <v>51500</v>
@@ -1447,25 +1446,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>73500</v>
+        <v>-16600</v>
       </c>
       <c r="E18" s="3">
-        <v>112700</v>
+        <v>-16600</v>
       </c>
       <c r="F18" s="3">
-        <v>53800</v>
+        <v>50800</v>
       </c>
       <c r="G18" s="3">
-        <v>59900</v>
+        <v>50800</v>
       </c>
       <c r="H18" s="3">
-        <v>240500</v>
+        <v>16300</v>
       </c>
       <c r="I18" s="3">
-        <v>434400</v>
+        <v>16300</v>
       </c>
       <c r="J18" s="3">
-        <v>120600</v>
+        <v>51000</v>
       </c>
       <c r="K18" s="3">
         <v>32400</v>
@@ -1553,25 +1552,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-24100</v>
+        <v>-3200</v>
       </c>
       <c r="E20" s="3">
-        <v>3800</v>
+        <v>-3200</v>
       </c>
       <c r="F20" s="3">
-        <v>9400</v>
+        <v>-5700</v>
       </c>
       <c r="G20" s="3">
-        <v>51700</v>
+        <v>-5700</v>
       </c>
       <c r="H20" s="3">
-        <v>394300</v>
+        <v>-4300</v>
       </c>
       <c r="I20" s="3">
-        <v>274800</v>
+        <v>-4300</v>
       </c>
       <c r="J20" s="3">
-        <v>319500</v>
+        <v>-4500</v>
       </c>
       <c r="K20" s="3">
         <v>105400</v>
@@ -1629,26 +1628,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="F21" s="3">
+        <v>56500</v>
+      </c>
+      <c r="G21" s="3">
+        <v>56500</v>
+      </c>
+      <c r="H21" s="3">
+        <v>20600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>20600</v>
+      </c>
+      <c r="J21" s="3">
+        <v>55500</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1706,26 +1705,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>4600</v>
-      </c>
-      <c r="E22" s="3">
-        <v>3600</v>
-      </c>
-      <c r="F22" s="3">
-        <v>500</v>
-      </c>
-      <c r="G22" s="3">
-        <v>300</v>
-      </c>
-      <c r="H22" s="3">
-        <v>6400</v>
-      </c>
-      <c r="I22" s="3">
-        <v>6400</v>
-      </c>
-      <c r="J22" s="3">
-        <v>3900</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>3000</v>
@@ -1784,25 +1783,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>44700</v>
+        <v>22400</v>
       </c>
       <c r="E23" s="3">
-        <v>113000</v>
+        <v>22400</v>
       </c>
       <c r="F23" s="3">
-        <v>62600</v>
+        <v>56500</v>
       </c>
       <c r="G23" s="3">
-        <v>111300</v>
+        <v>56500</v>
       </c>
       <c r="H23" s="3">
-        <v>628400</v>
+        <v>31300</v>
       </c>
       <c r="I23" s="3">
-        <v>702800</v>
+        <v>31300</v>
       </c>
       <c r="J23" s="3">
-        <v>436100</v>
+        <v>55500</v>
       </c>
       <c r="K23" s="3">
         <v>134800</v>
@@ -1861,25 +1860,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-2900</v>
+        <v>-1500</v>
       </c>
       <c r="E24" s="3">
-        <v>7200</v>
+        <v>-1500</v>
       </c>
       <c r="F24" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G24" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J24" s="3">
         <v>4500</v>
-      </c>
-      <c r="G24" s="3">
-        <v>8900</v>
-      </c>
-      <c r="H24" s="3">
-        <v>36200</v>
-      </c>
-      <c r="I24" s="3">
-        <v>73100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>25500</v>
       </c>
       <c r="K24" s="3">
         <v>10400</v>
@@ -2015,25 +2014,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>47600</v>
+        <v>23800</v>
       </c>
       <c r="E26" s="3">
-        <v>105700</v>
+        <v>23800</v>
       </c>
       <c r="F26" s="3">
-        <v>58100</v>
+        <v>52900</v>
       </c>
       <c r="G26" s="3">
-        <v>102300</v>
+        <v>52900</v>
       </c>
       <c r="H26" s="3">
-        <v>592200</v>
+        <v>29100</v>
       </c>
       <c r="I26" s="3">
-        <v>629700</v>
+        <v>29100</v>
       </c>
       <c r="J26" s="3">
-        <v>410600</v>
+        <v>51100</v>
       </c>
       <c r="K26" s="3">
         <v>124400</v>
@@ -2092,25 +2091,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>37900</v>
+        <v>23200</v>
       </c>
       <c r="E27" s="3">
-        <v>96600</v>
+        <v>23200</v>
       </c>
       <c r="F27" s="3">
-        <v>47000</v>
+        <v>48300</v>
       </c>
       <c r="G27" s="3">
-        <v>94700</v>
+        <v>48300</v>
       </c>
       <c r="H27" s="3">
-        <v>529400</v>
+        <v>31400</v>
       </c>
       <c r="I27" s="3">
-        <v>567000</v>
+        <v>31400</v>
       </c>
       <c r="J27" s="3">
-        <v>379200</v>
+        <v>47300</v>
       </c>
       <c r="K27" s="3">
         <v>93100</v>
@@ -2477,25 +2476,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>24100</v>
+        <v>3200</v>
       </c>
       <c r="E32" s="3">
-        <v>-3800</v>
+        <v>3200</v>
       </c>
       <c r="F32" s="3">
-        <v>-9400</v>
+        <v>5700</v>
       </c>
       <c r="G32" s="3">
-        <v>-51700</v>
+        <v>5700</v>
       </c>
       <c r="H32" s="3">
-        <v>-394300</v>
+        <v>4300</v>
       </c>
       <c r="I32" s="3">
-        <v>-274800</v>
+        <v>4300</v>
       </c>
       <c r="J32" s="3">
-        <v>-319500</v>
+        <v>4500</v>
       </c>
       <c r="K32" s="3">
         <v>-105400</v>
@@ -2554,25 +2553,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>37900</v>
+        <v>20000</v>
       </c>
       <c r="E33" s="3">
-        <v>96600</v>
+        <v>20000</v>
       </c>
       <c r="F33" s="3">
-        <v>47000</v>
+        <v>51500</v>
       </c>
       <c r="G33" s="3">
-        <v>94700</v>
+        <v>51500</v>
       </c>
       <c r="H33" s="3">
-        <v>529400</v>
+        <v>27500</v>
       </c>
       <c r="I33" s="3">
-        <v>567000</v>
+        <v>27500</v>
       </c>
       <c r="J33" s="3">
-        <v>379200</v>
+        <v>51200</v>
       </c>
       <c r="K33" s="3">
         <v>93100</v>
@@ -2708,25 +2707,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>37900</v>
+        <v>20000</v>
       </c>
       <c r="E35" s="3">
-        <v>96600</v>
+        <v>20000</v>
       </c>
       <c r="F35" s="3">
-        <v>47000</v>
+        <v>51500</v>
       </c>
       <c r="G35" s="3">
-        <v>94700</v>
+        <v>51500</v>
       </c>
       <c r="H35" s="3">
-        <v>529400</v>
+        <v>27500</v>
       </c>
       <c r="I35" s="3">
-        <v>567000</v>
+        <v>27500</v>
       </c>
       <c r="J35" s="3">
-        <v>379200</v>
+        <v>51200</v>
       </c>
       <c r="K35" s="3">
         <v>93100</v>
@@ -2793,22 +2792,22 @@
         <v>45291</v>
       </c>
       <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>44834</v>
+      </c>
+      <c r="J38" s="2">
         <v>44742</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44377</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44196</v>
       </c>
       <c r="K38" s="2">
         <v>44104</v>
@@ -2925,25 +2924,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>121300</v>
+        <v>120200</v>
       </c>
       <c r="E41" s="3">
-        <v>162100</v>
+        <v>120200</v>
       </c>
       <c r="F41" s="3">
-        <v>139500</v>
+        <v>161500</v>
       </c>
       <c r="G41" s="3">
-        <v>237700</v>
+        <v>161500</v>
       </c>
       <c r="H41" s="3">
-        <v>84900</v>
+        <v>138300</v>
       </c>
       <c r="I41" s="3">
-        <v>586400</v>
+        <v>138300</v>
       </c>
       <c r="J41" s="3">
-        <v>651300</v>
+        <v>17900</v>
       </c>
       <c r="K41" s="3">
         <v>647800</v>
@@ -3001,26 +3000,26 @@
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>5</v>
+      <c r="D42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F42" s="3">
+        <v>218200</v>
+      </c>
+      <c r="G42" s="3">
+        <v>218200</v>
+      </c>
+      <c r="H42" s="3">
+        <v>186300</v>
+      </c>
+      <c r="I42" s="3">
+        <v>186300</v>
       </c>
       <c r="J42" s="3">
-        <v>62500</v>
+        <v>196600</v>
       </c>
       <c r="K42" s="3">
         <v>1069900</v>
@@ -3079,25 +3078,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1064900</v>
+        <v>1078300</v>
       </c>
       <c r="E43" s="3">
+        <v>1078300</v>
+      </c>
+      <c r="F43" s="3">
         <v>546800</v>
       </c>
-      <c r="F43" s="3">
-        <v>311600</v>
-      </c>
       <c r="G43" s="3">
-        <v>5159000</v>
+        <v>546800</v>
       </c>
       <c r="H43" s="3">
-        <v>286200</v>
+        <v>433900</v>
       </c>
       <c r="I43" s="3">
-        <v>7027000</v>
+        <v>433900</v>
       </c>
       <c r="J43" s="3">
-        <v>6555700</v>
+        <v>657400</v>
       </c>
       <c r="K43" s="3">
         <v>7495600</v>
@@ -3155,26 +3154,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3233,25 +3232,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>16600</v>
+        <v>3000</v>
       </c>
       <c r="E45" s="3">
-        <v>399000</v>
+        <v>3000</v>
       </c>
       <c r="F45" s="3">
-        <v>309700</v>
+        <v>181200</v>
       </c>
       <c r="G45" s="3">
-        <v>1778300</v>
+        <v>181200</v>
       </c>
       <c r="H45" s="3">
-        <v>127200</v>
+        <v>1900</v>
       </c>
       <c r="I45" s="3">
-        <v>1018700</v>
+        <v>1900</v>
       </c>
       <c r="J45" s="3">
-        <v>1047700</v>
+        <v>42400</v>
       </c>
       <c r="K45" s="3">
         <v>1020900</v>
@@ -3313,22 +3312,22 @@
         <v>1202700</v>
       </c>
       <c r="E46" s="3">
+        <v>1202700</v>
+      </c>
+      <c r="F46" s="3">
         <v>1107800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
+        <v>1107800</v>
+      </c>
+      <c r="H46" s="3">
         <v>760900</v>
       </c>
-      <c r="G46" s="3">
-        <v>7175000</v>
-      </c>
-      <c r="H46" s="3">
-        <v>498400</v>
-      </c>
       <c r="I46" s="3">
-        <v>8632100</v>
+        <v>760900</v>
       </c>
       <c r="J46" s="3">
-        <v>8317200</v>
+        <v>914300</v>
       </c>
       <c r="K46" s="3">
         <v>10234300</v>
@@ -3387,25 +3386,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>15800</v>
+        <v>95400</v>
       </c>
       <c r="E47" s="3">
-        <v>99600</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>5</v>
+        <v>95400</v>
+      </c>
+      <c r="F47" s="3">
+        <v>243700</v>
       </c>
       <c r="G47" s="3">
-        <v>300200</v>
+        <v>243700</v>
       </c>
       <c r="H47" s="3">
-        <v>211300</v>
+        <v>195300</v>
       </c>
       <c r="I47" s="3">
-        <v>910100</v>
+        <v>195300</v>
       </c>
       <c r="J47" s="3">
-        <v>878500</v>
+        <v>185000</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>5</v>
@@ -3467,22 +3466,22 @@
         <v>70100</v>
       </c>
       <c r="E48" s="3">
+        <v>70100</v>
+      </c>
+      <c r="F48" s="3">
         <v>242700</v>
       </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
       <c r="G48" s="3">
-        <v>3800</v>
+        <v>242700</v>
       </c>
       <c r="H48" s="3">
         <v>0</v>
       </c>
       <c r="I48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -3544,22 +3543,22 @@
         <v>118400</v>
       </c>
       <c r="E49" s="3">
+        <v>118400</v>
+      </c>
+      <c r="F49" s="3">
         <v>92700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
+        <v>92700</v>
+      </c>
+      <c r="H49" s="3">
         <v>104500</v>
       </c>
-      <c r="G49" s="3">
-        <v>796400</v>
-      </c>
-      <c r="H49" s="3">
-        <v>1900</v>
-      </c>
       <c r="I49" s="3">
-        <v>15200</v>
+        <v>104500</v>
       </c>
       <c r="J49" s="3">
-        <v>15200</v>
+        <v>101500</v>
       </c>
       <c r="K49" s="3">
         <v>15200</v>
@@ -3771,26 +3770,26 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>79600</v>
-      </c>
-      <c r="E52" s="3">
-        <v>144100</v>
-      </c>
-      <c r="F52" s="3">
-        <v>195300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1436700</v>
-      </c>
-      <c r="H52" s="3">
-        <v>357400</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1523800</v>
+      <c r="D52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J52" s="3">
-        <v>1315300</v>
+        <v>36300</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>5</v>
@@ -3929,22 +3928,22 @@
         <v>1486600</v>
       </c>
       <c r="E54" s="3">
+        <v>1486600</v>
+      </c>
+      <c r="F54" s="3">
         <v>1687000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
+        <v>1687000</v>
+      </c>
+      <c r="H54" s="3">
         <v>1060700</v>
       </c>
-      <c r="G54" s="3">
-        <v>9712100</v>
-      </c>
-      <c r="H54" s="3">
-        <v>857700</v>
-      </c>
       <c r="I54" s="3">
-        <v>11081200</v>
+        <v>1060700</v>
       </c>
       <c r="J54" s="3">
-        <v>10526300</v>
+        <v>1237600</v>
       </c>
       <c r="K54" s="3">
         <v>10249500</v>
@@ -4061,25 +4060,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>28600</v>
+        <v>9400</v>
       </c>
       <c r="E57" s="3">
-        <v>43500</v>
+        <v>9400</v>
       </c>
       <c r="F57" s="3">
-        <v>27500</v>
+        <v>9500</v>
       </c>
       <c r="G57" s="3">
-        <v>468200</v>
+        <v>9500</v>
       </c>
       <c r="H57" s="3">
-        <v>31700</v>
+        <v>10600</v>
       </c>
       <c r="I57" s="3">
-        <v>320900</v>
+        <v>10600</v>
       </c>
       <c r="J57" s="3">
-        <v>283000</v>
+        <v>10500</v>
       </c>
       <c r="K57" s="3">
         <v>421900</v>
@@ -4138,25 +4137,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>65800</v>
+        <v>99300</v>
       </c>
       <c r="E58" s="3">
+        <v>99300</v>
+      </c>
+      <c r="F58" s="3">
         <v>66000</v>
       </c>
-      <c r="F58" s="3">
-        <v>177000</v>
-      </c>
       <c r="G58" s="3">
-        <v>163900</v>
+        <v>66000</v>
       </c>
       <c r="H58" s="3">
-        <v>49900</v>
+        <v>20100</v>
       </c>
       <c r="I58" s="3">
-        <v>232500</v>
+        <v>20100</v>
       </c>
       <c r="J58" s="3">
-        <v>232300</v>
+        <v>20900</v>
       </c>
       <c r="K58" s="3">
         <v>232300</v>
@@ -4215,25 +4214,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>62600</v>
+        <v>34200</v>
       </c>
       <c r="E59" s="3">
-        <v>67100</v>
+        <v>34200</v>
       </c>
       <c r="F59" s="3">
-        <v>7000</v>
+        <v>101100</v>
       </c>
       <c r="G59" s="3">
-        <v>159700</v>
+        <v>101100</v>
       </c>
       <c r="H59" s="3">
-        <v>17500</v>
+        <v>9200</v>
       </c>
       <c r="I59" s="3">
-        <v>99900</v>
+        <v>9200</v>
       </c>
       <c r="J59" s="3">
-        <v>170600</v>
+        <v>57400</v>
       </c>
       <c r="K59" s="3">
         <v>97800</v>
@@ -4295,22 +4294,22 @@
         <v>157100</v>
       </c>
       <c r="E60" s="3">
+        <v>157100</v>
+      </c>
+      <c r="F60" s="3">
         <v>176700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
+        <v>176700</v>
+      </c>
+      <c r="H60" s="3">
         <v>54500</v>
       </c>
-      <c r="G60" s="3">
-        <v>791900</v>
-      </c>
-      <c r="H60" s="3">
-        <v>99100</v>
-      </c>
       <c r="I60" s="3">
-        <v>653300</v>
+        <v>54500</v>
       </c>
       <c r="J60" s="3">
-        <v>685900</v>
+        <v>100900</v>
       </c>
       <c r="K60" s="3">
         <v>752000</v>
@@ -4375,19 +4374,19 @@
         <v>30400</v>
       </c>
       <c r="F61" s="3">
+        <v>30400</v>
+      </c>
+      <c r="G61" s="3">
+        <v>30400</v>
+      </c>
+      <c r="H61" s="3">
         <v>500</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
-      <c r="H61" s="3">
-        <v>14400</v>
-      </c>
       <c r="I61" s="3">
-        <v>107400</v>
+        <v>500</v>
       </c>
       <c r="J61" s="3">
-        <v>103300</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>101400</v>
@@ -4445,26 +4444,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>5600</v>
-      </c>
-      <c r="E62" s="3">
-        <v>2600</v>
-      </c>
-      <c r="F62" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G62" s="3">
-        <v>76700</v>
-      </c>
-      <c r="H62" s="3">
-        <v>1800</v>
-      </c>
-      <c r="I62" s="3">
-        <v>13700</v>
-      </c>
-      <c r="J62" s="3">
-        <v>13000</v>
+      <c r="D62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K62" s="3">
         <v>20700</v>
@@ -4754,25 +4753,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>200100</v>
+        <v>193000</v>
       </c>
       <c r="E66" s="3">
-        <v>343600</v>
+        <v>193000</v>
       </c>
       <c r="F66" s="3">
-        <v>90000</v>
+        <v>209800</v>
       </c>
       <c r="G66" s="3">
-        <v>973700</v>
+        <v>209800</v>
       </c>
       <c r="H66" s="3">
-        <v>117600</v>
+        <v>58300</v>
       </c>
       <c r="I66" s="3">
-        <v>789900</v>
+        <v>58300</v>
       </c>
       <c r="J66" s="3">
-        <v>802100</v>
+        <v>110700</v>
       </c>
       <c r="K66" s="3">
         <v>874000</v>
@@ -5168,25 +5167,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1784200</v>
+        <v>859800</v>
       </c>
       <c r="E72" s="3">
-        <v>1804500</v>
+        <v>859800</v>
       </c>
       <c r="F72" s="3">
-        <v>1701800</v>
+        <v>809400</v>
       </c>
       <c r="G72" s="3">
-        <v>11965900</v>
+        <v>809400</v>
       </c>
       <c r="H72" s="3">
-        <v>1153100</v>
+        <v>712900</v>
       </c>
       <c r="I72" s="3">
-        <v>8455300</v>
+        <v>712900</v>
       </c>
       <c r="J72" s="3">
-        <v>7888300</v>
+        <v>661500</v>
       </c>
       <c r="K72" s="3">
         <v>7509200</v>
@@ -5479,22 +5478,22 @@
         <v>1286500</v>
       </c>
       <c r="E76" s="3">
+        <v>1286500</v>
+      </c>
+      <c r="F76" s="3">
         <v>1343300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>1343300</v>
+      </c>
+      <c r="H76" s="3">
         <v>970700</v>
       </c>
-      <c r="G76" s="3">
-        <v>8738400</v>
-      </c>
-      <c r="H76" s="3">
-        <v>740100</v>
-      </c>
       <c r="I76" s="3">
-        <v>10291300</v>
+        <v>970700</v>
       </c>
       <c r="J76" s="3">
-        <v>9724200</v>
+        <v>1113500</v>
       </c>
       <c r="K76" s="3">
         <v>9375400</v>
@@ -5638,22 +5637,22 @@
         <v>45291</v>
       </c>
       <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>44834</v>
+      </c>
+      <c r="J80" s="2">
         <v>44742</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44377</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44196</v>
       </c>
       <c r="K80" s="2">
         <v>44104</v>
@@ -5712,25 +5711,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>37900</v>
+        <v>20000</v>
       </c>
       <c r="E81" s="3">
-        <v>96600</v>
+        <v>20000</v>
       </c>
       <c r="F81" s="3">
-        <v>47000</v>
+        <v>51500</v>
       </c>
       <c r="G81" s="3">
-        <v>94700</v>
+        <v>51500</v>
       </c>
       <c r="H81" s="3">
-        <v>529400</v>
+        <v>27500</v>
       </c>
       <c r="I81" s="3">
-        <v>567000</v>
+        <v>27500</v>
       </c>
       <c r="J81" s="3">
-        <v>379200</v>
+        <v>51200</v>
       </c>
       <c r="K81" s="3">
         <v>93100</v>
@@ -5817,26 +5816,26 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -6279,26 +6278,26 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -6385,26 +6384,26 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -6616,26 +6615,26 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -6722,26 +6721,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7030,26 +7029,26 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -7107,26 +7106,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7184,26 +7183,26 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/AMTD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMTD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
   <si>
     <t>AMTD</t>
   </si>
@@ -656,198 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44104</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44012</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43830</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43738</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43646</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43646</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43555</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43465</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43373</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43281</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43190</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43100</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43008</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42825</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42735</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="D8" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>14900</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3">
         <v>62200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>62200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>28400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>28400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>58600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>83900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>69100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>20100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>18500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>25000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1491000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1451000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1516000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1398000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1382000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1415000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1257000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>983000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>931000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>904000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>859000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>830000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -887,21 +901,21 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>59000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>53000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>49000</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>5</v>
       </c>
@@ -923,38 +937,44 @@
       <c r="AA9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>14900</v>
+      </c>
+      <c r="F10" s="3">
         <v>-800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>62200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>62200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>28400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>28400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>58600</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -964,21 +984,21 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
         <v>1432000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1398000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1467000</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1000,8 +1020,14 @@
       <c r="AA10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,35 +1055,37 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="3">
         <v>400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>400</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J12" s="3">
         <v>400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>400</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1106,8 +1134,14 @@
       <c r="AA12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,35 +1217,41 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>-35800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-35800</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>-10700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-10700</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1224,44 +1264,50 @@
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>-60000</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
         <v>1000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>1000</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1269,10 +1315,10 @@
         <v>400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
@@ -1302,43 +1348,49 @@
         <v>0</v>
       </c>
       <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
         <v>69000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>67000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>66000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>70000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>69000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>72000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>72000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>50000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>44000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>44000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>43000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>45000</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1415,176 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>11600</v>
+      </c>
+      <c r="F17" s="3">
         <v>15700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>15700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>11400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>11400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>12100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>12100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>7600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>51500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>16500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>7300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>6900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>6900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>711000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>746000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>720000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>764000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>751000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1019000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>921000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>622000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>538000</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>546000</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>506000</v>
       </c>
       <c r="AA17" s="3">
         <v>546000</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3">
+        <v>506000</v>
+      </c>
+      <c r="AC17" s="3">
+        <v>546000</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-16600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-16600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>50800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>50800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>16300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>16300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>51000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>32400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>52600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>12900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>11600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>18200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>780000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>705000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>796000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>634000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>631000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>396000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>336000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>361000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>393000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>358000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>353000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>284000</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,74 +1612,76 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-3200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-3200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-5700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-5700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-4300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-4300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-4500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>105400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>4500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>2400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>36500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>14800</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>14000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>2000</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-13000</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
@@ -1623,85 +1691,97 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>22400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-13000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-13400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>56500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>56500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>20600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>20600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>55500</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="3">
         <v>15300</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>849000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>772000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>876000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>706000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>700000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>468000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>395000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>411000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>437000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>402000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>396000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>329000</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1726,213 +1806,231 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" s="3">
         <v>3000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>1900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>1500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>37000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>37000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>32000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>27000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>28000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>24000</v>
-      </c>
-      <c r="V22" s="3">
-        <v>20000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>23000</v>
       </c>
       <c r="X22" s="3">
         <v>20000</v>
       </c>
       <c r="Y22" s="3">
-        <v>14000</v>
+        <v>23000</v>
       </c>
       <c r="Z22" s="3">
-        <v>14000</v>
+        <v>20000</v>
       </c>
       <c r="AA22" s="3">
         <v>14000</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>22000</v>
+      </c>
+      <c r="F23" s="3">
         <v>22400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>22400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>56500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>56500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>31300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>31300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>55500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>134800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>55200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>13800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>47400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>32300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>743000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>668000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>778000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>609000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>603000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>372000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>303000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>338000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>373000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>344000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>339000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>270000</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>900</v>
+      </c>
+      <c r="E24" s="3">
+        <v>900</v>
+      </c>
+      <c r="F24" s="3">
         <v>-1500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-1500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>3600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>3600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>2200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>2200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>4500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>10400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-22200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>2400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>8200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>4200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>188000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>169000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>174000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>155000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>155000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>101000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>74000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>127000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>142000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>130000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>123000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>85000</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2106,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>21000</v>
+      </c>
+      <c r="F26" s="3">
         <v>23800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>23800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>52900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>52900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>29100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>29100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>51100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>124400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>77400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>11400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>39200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>28100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>555000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>499000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>604000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>454000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>448000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>271000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>229000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>211000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>231000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>214000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>216000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>20300</v>
+      </c>
+      <c r="F27" s="3">
         <v>23200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>23200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>48300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>48300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>31400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>31400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>47300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>93100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>75300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>11400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>39200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>28100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>555000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>499000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>604000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>454000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>448000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>271000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>229000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>211000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>231000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>214000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>216000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2355,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2280,33 +2402,33 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>3000</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>68000</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2316,8 +2438,14 @@
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2521,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,74 +2604,80 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E32" s="3">
+        <v>18700</v>
+      </c>
+      <c r="F32" s="3">
         <v>3200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>3200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>5700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>5700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>4300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>4300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>4500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-105400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-4500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-2400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-36500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-14800</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-14000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-2000</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>13000</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -2547,85 +2687,97 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>21300</v>
+      </c>
+      <c r="F33" s="3">
         <v>20000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>20000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>51500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>51500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>27500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>27500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>51200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>93100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>75300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>11400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>39200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>28100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>555000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>499000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>604000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>454000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>451000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>271000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>297000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>211000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>231000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>214000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>216000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2853,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>21300</v>
+      </c>
+      <c r="F35" s="3">
         <v>20000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>20000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>51500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>51500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>27500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>27500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>51200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>93100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>75300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>11400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>39200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>28100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>555000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>499000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>604000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>454000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>451000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>271000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>297000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>211000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>231000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>214000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>216000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44104</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44012</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43830</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43738</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43646</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43646</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43555</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43465</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43373</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43281</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43190</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43100</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43008</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42825</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42735</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +3059,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,130 +3090,138 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>78600</v>
+      </c>
+      <c r="F41" s="3">
         <v>120200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>120200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>161500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>161500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>138300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>138300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>17900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>647800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>147900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>128900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>122000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>112500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2953000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2674000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>5117000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>2690000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1343000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1373000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1644000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1472000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2880000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2231000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1662000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1855000</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>600</v>
+      </c>
+      <c r="E42" s="3">
+        <v>600</v>
+      </c>
+      <c r="F42" s="3">
         <v>1000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>218200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>218200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>186300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>186300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>196600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>1069900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>129500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>200400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>223100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>246000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -3072,85 +3252,97 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1121800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1121800</v>
+      </c>
+      <c r="F43" s="3">
         <v>1078300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1078300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>546800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>546800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>433900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>433900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>657400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>7495600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>894200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>569500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>446400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>670500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>23014000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>22790000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>21312000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>24445000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>24345000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>22709000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>20287000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>18796000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>15020000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>13393000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>13277000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>13397000</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3175,11 +3367,11 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3226,130 +3418,142 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>18500</v>
+      </c>
+      <c r="F45" s="3">
         <v>3000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>181200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>181200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>42400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1020900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>121300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>153000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>109800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>31900</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
-      <c r="T45" s="3">
+      <c r="S45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+      <c r="V45" s="3">
         <v>4609000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>6863000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>10136000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>10446000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>7328000</v>
       </c>
-      <c r="Y45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>0</v>
-      </c>
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1219400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1219400</v>
+      </c>
+      <c r="F46" s="3">
         <v>1202700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1202700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1107800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1107800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>760900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>760900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>914300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>10234300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1292900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1051700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>901300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1060900</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3380,38 +3584,44 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>93200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>93200</v>
+      </c>
+      <c r="F47" s="3">
         <v>95400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>95400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>243700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>243700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>195300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>195300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>185000</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3421,74 +3631,80 @@
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R47" s="3">
         <v>1447000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1053000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>993000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>640000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>682000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>901000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>692000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>1249000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>1154000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>9831000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>10187000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>9817000</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>271900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>271900</v>
+      </c>
+      <c r="F48" s="3">
         <v>70100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>70100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>242700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>242700</v>
       </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
       <c r="J48" s="3">
+        <v>0</v>
+      </c>
+      <c r="K48" s="3">
+        <v>0</v>
+      </c>
+      <c r="L48" s="3">
         <v>500</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
-      </c>
-      <c r="L48" s="3">
-        <v>0</v>
-      </c>
       <c r="M48" s="3">
         <v>0</v>
       </c>
@@ -3499,75 +3715,81 @@
         <v>0</v>
       </c>
       <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3">
         <v>833000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>812000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>797000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>792000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>778000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>801000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>780000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>752000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>592000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>555000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>531000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>526000</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>118700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>118700</v>
+      </c>
+      <c r="F49" s="3">
         <v>118400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>118400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>92700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>92700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>104500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>104500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>101500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>15200</v>
-      </c>
-      <c r="L49" s="3">
-        <v>1900</v>
-      </c>
-      <c r="M49" s="3">
-        <v>1900</v>
       </c>
       <c r="N49" s="3">
         <v>1900</v>
@@ -3576,43 +3798,49 @@
         <v>1900</v>
       </c>
       <c r="P49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="R49" s="3">
         <v>5463000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>5494000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>5525000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>5556000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>5561000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>5597000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>5629000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>5683000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>2985000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>3004000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>3023000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>3042000</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3916,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,8 +3999,14 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3788,15 +4028,15 @@
       <c r="I52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L52" s="3">
         <v>36300</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3806,24 +4046,24 @@
       <c r="O52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R52" s="3">
         <v>7124000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>5580000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>3185000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>3185000</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
-      </c>
-      <c r="U52" s="3">
-        <v>0</v>
-      </c>
       <c r="V52" s="3">
         <v>0</v>
       </c>
@@ -3842,8 +4082,14 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,85 +4165,97 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1703200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1703200</v>
+      </c>
+      <c r="F54" s="3">
         <v>1486600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1486600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1687000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1687000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1060700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1060700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1237600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>10249500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1294800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1053700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>903200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1062800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>41119000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>38679000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>37191000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>37520000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>37511000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>38410000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>39412000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>38627000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>30110000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>29165000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>28834000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>28818000</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4283,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,207 +4314,221 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F57" s="3">
         <v>9400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>9400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>9500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>9500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>10600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>10600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>10500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>421900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>82300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>71100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>62400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>460100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>28833000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>26621000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>25139000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>26805000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>26859000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>27889000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>29119000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>28535000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>21821000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>21806000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>21582000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>21669000</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>30200</v>
+      </c>
+      <c r="F58" s="3">
         <v>99300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>99300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>66000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>66000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>20100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>20100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>20900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>232300</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>40500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>41000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>41100</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>96000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>97000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>318000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>147000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>97000</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>103000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>103000</v>
+      </c>
+      <c r="F59" s="3">
         <v>34200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>34200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>101100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>101100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>9200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>9200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>57400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>97800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>11200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>26300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>9700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>7500</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4264,11 +4538,11 @@
       <c r="T59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U59" s="3">
-        <v>0</v>
-      </c>
-      <c r="V59" s="3">
-        <v>0</v>
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
@@ -4285,53 +4559,59 @@
       <c r="AA59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>134500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>134500</v>
+      </c>
+      <c r="F60" s="3">
         <v>157100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>157100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>176700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>176700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>54500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>54500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>100900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>752000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>93500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>137900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>113100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>508800</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -4362,16 +4642,22 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>30400</v>
+        <v>235100</v>
       </c>
       <c r="E61" s="3">
-        <v>30400</v>
+        <v>235100</v>
       </c>
       <c r="F61" s="3">
         <v>30400</v>
@@ -4380,75 +4666,81 @@
         <v>30400</v>
       </c>
       <c r="H61" s="3">
+        <v>30400</v>
+      </c>
+      <c r="I61" s="3">
+        <v>30400</v>
+      </c>
+      <c r="J61" s="3">
         <v>500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>500</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>101400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>12800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>12200</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>3574000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>3520000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>3484000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>2439000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>2456000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>2477000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>2531000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>2555000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2561000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1765000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>1769000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>1817000</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>5</v>
+      <c r="D62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1500</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>5</v>
@@ -4465,59 +4757,65 @@
       <c r="J62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M62" s="3">
         <v>20700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>2700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>33600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>31000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>25000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>219000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>215000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>211000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>177000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>163000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>131000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>182000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>193000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>268000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>269000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>284000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>281000</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4891,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4974,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,85 +5057,97 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>376700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>376700</v>
+      </c>
+      <c r="F66" s="3">
         <v>193000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>193000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>209800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>209800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>58300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>58300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>110700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>874000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>108900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>183700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>144000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>533700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>32626000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>30356000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>28834000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>29517000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>29575000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>30815000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>31979000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>31380000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>24650000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>23840000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>23635000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>23767000</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5175,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5254,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5337,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5420,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,85 +5503,97 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>900400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>900400</v>
+      </c>
+      <c r="F72" s="3">
         <v>859800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>859800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>809400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>809400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>712900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>712900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>661500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>7509200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>950700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>869900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>759100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>529100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>8194000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>7805000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>7475000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>7011000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>6673000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>6341000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>6189000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>6011000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>5895000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>5759000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>5640000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>5518000</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5669,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5752,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,85 +5835,97 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1329900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1329900</v>
+      </c>
+      <c r="F76" s="3">
         <v>1286500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1286500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1343300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1343300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>970700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>970700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1113500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>9375400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1185900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>870000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>759200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>529100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>8493000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>8323000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>8357000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>8003000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>7936000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>7595000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>7433000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>7247000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>5460000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>5325000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>5199000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>5051000</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +6001,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44104</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44012</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43830</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43738</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43646</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43646</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43555</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43465</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43373</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43281</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43190</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43100</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43008</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42825</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42735</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>21300</v>
+      </c>
+      <c r="F81" s="3">
         <v>20000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>20000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>51500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>51500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>27500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>27500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>51200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>93100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>75300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>11400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>39200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>28100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>555000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>499000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>604000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>454000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>451000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>271000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>297000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>211000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>231000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>214000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>216000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,8 +6207,10 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5837,11 +6235,11 @@
       <c r="J83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -5853,43 +6251,49 @@
         <v>0</v>
       </c>
       <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
         <v>69000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>67000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>66000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>70000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>69000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>72000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>72000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>50000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>44000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>44000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>43000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>45000</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6369,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6452,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6535,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6618,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,8 +6701,14 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6299,11 +6733,11 @@
       <c r="J89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -6315,43 +6749,49 @@
         <v>0</v>
       </c>
       <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
         <v>2438000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>573000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>2762000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>1821000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>349000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>124000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-386000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>23000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>27000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>718000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-81000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>436000</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,8 +6819,10 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6405,11 +6847,11 @@
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -6421,43 +6863,49 @@
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-59000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-48000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-44000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-63000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-47000</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-56000</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-63000</v>
       </c>
       <c r="W91" s="3">
         <v>-56000</v>
       </c>
       <c r="X91" s="3">
+        <v>-63000</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-62000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-100000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-27000</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6981,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,8 +7064,14 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6636,11 +7096,11 @@
       <c r="J94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -6652,43 +7112,49 @@
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-195000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-48000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-426000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-66000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-35000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-440000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>633000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-1406000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-62000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-50000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-29000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-384000</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +7182,10 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6742,11 +7210,11 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6758,43 +7226,49 @@
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-166000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-169000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-168000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-120000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-119000</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-119000</v>
       </c>
       <c r="V96" s="3">
         <v>-119000</v>
       </c>
       <c r="W96" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="X96" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-94000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-95000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-95000</v>
       </c>
       <c r="Z96" s="3">
         <v>-95000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7344,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7427,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,8 +7510,14 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7050,11 +7542,11 @@
       <c r="J100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -7066,43 +7558,49 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-409000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-552000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>594000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-408000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-344000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>45000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-75000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-37000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>685000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-97000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-74000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-114000</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7127,11 +7625,11 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7178,8 +7676,14 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7204,11 +7708,11 @@
       <c r="J102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
@@ -7220,39 +7724,45 @@
         <v>0</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>1834000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-27000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>2930000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>1347000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-30000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-271000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>172000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1408000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>649000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>569000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-193000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-62000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMTD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMTD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
   <si>
     <t>AMTD</t>
   </si>
@@ -656,212 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44104</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44012</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43830</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43738</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43646</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43646</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43555</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43465</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43373</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43190</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43008</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42916</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42825</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42735</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>18700</v>
+      </c>
+      <c r="F8" s="3">
         <v>14900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>14900</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H8" s="3">
+        <v>8600</v>
+      </c>
+      <c r="I8" s="3">
+        <v>8600</v>
+      </c>
+      <c r="J8" s="3">
         <v>62200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>62200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>28400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>28400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>58600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>83900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>69100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>20100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>18500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>25000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1491000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1451000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1516000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1398000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1382000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1415000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1257000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>983000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>931000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>904000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>859000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>830000</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -907,21 +920,21 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>59000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>53000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>49000</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>5</v>
       </c>
@@ -943,44 +956,50 @@
       <c r="AC9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>18700</v>
+      </c>
+      <c r="F10" s="3">
         <v>14900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>14900</v>
       </c>
-      <c r="F10" s="3">
-        <v>-800</v>
-      </c>
-      <c r="G10" s="3">
-        <v>-800</v>
-      </c>
       <c r="H10" s="3">
+        <v>8600</v>
+      </c>
+      <c r="I10" s="3">
+        <v>8600</v>
+      </c>
+      <c r="J10" s="3">
         <v>62200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>62200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>28400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>28400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>58600</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
@@ -990,21 +1009,21 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>1432000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1398000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1467000</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1026,8 +1045,14 @@
       <c r="AC10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,41 +1082,43 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="D12" s="3">
+        <v>100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>100</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" s="3">
         <v>400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>400</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L12" s="3">
         <v>400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>400</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1140,8 +1167,14 @@
       <c r="AC12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,41 +1256,47 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>-35800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-35800</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>-10700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-10700</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1270,49 +1309,55 @@
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>-60000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="3">
         <v>1000</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>1000</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="E15" s="3">
         <v>400</v>
@@ -1321,13 +1366,13 @@
         <v>400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1354,43 +1399,49 @@
         <v>0</v>
       </c>
       <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
         <v>69000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>67000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>66000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>70000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>69000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>72000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>72000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>50000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>44000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>44000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>43000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>45000</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1468,188 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>15700</v>
+      </c>
+      <c r="F17" s="3">
         <v>11600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>11600</v>
       </c>
-      <c r="F17" s="3">
-        <v>15700</v>
-      </c>
-      <c r="G17" s="3">
-        <v>15700</v>
-      </c>
       <c r="H17" s="3">
+        <v>16400</v>
+      </c>
+      <c r="I17" s="3">
+        <v>16400</v>
+      </c>
+      <c r="J17" s="3">
         <v>11400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>11400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>12100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>12100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>7600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>51500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>16500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>7300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>6900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>6900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>711000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>746000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>720000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>764000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>751000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1019000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>921000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>622000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>538000</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>546000</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>506000</v>
       </c>
       <c r="AC17" s="3">
         <v>546000</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3">
+        <v>506000</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>546000</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F18" s="3">
         <v>3200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>3200</v>
       </c>
-      <c r="F18" s="3">
-        <v>-16600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-16600</v>
-      </c>
       <c r="H18" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="J18" s="3">
         <v>50800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>50800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>16300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>16300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>51000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>32400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>52600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>12900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>11600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>18200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>780000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>705000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>796000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>634000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>631000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>396000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>336000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>361000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>393000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>358000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>353000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>284000</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,80 +1679,82 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-18700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-18700</v>
       </c>
-      <c r="F20" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-3200</v>
-      </c>
       <c r="H20" s="3">
+        <v>9500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>9500</v>
+      </c>
+      <c r="J20" s="3">
         <v>-5700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-5700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-4300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-4300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-4500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>105400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>4500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>2400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>36500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>14800</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>14000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>2000</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
@@ -1697,91 +1764,103 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F21" s="3">
         <v>22400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>22400</v>
       </c>
-      <c r="F21" s="3">
-        <v>-13000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-13400</v>
-      </c>
       <c r="H21" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="J21" s="3">
         <v>56500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>56500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>20600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>20600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>55500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
         <v>15300</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>849000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>772000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>876000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>706000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>700000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>468000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>395000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>411000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>437000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>402000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>396000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>329000</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1812,225 +1891,243 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O22" s="3">
         <v>3000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>1900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>1500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>37000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>37000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>32000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>27000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>28000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>24000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>20000</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>23000</v>
       </c>
       <c r="Z22" s="3">
         <v>20000</v>
       </c>
       <c r="AA22" s="3">
-        <v>14000</v>
+        <v>23000</v>
       </c>
       <c r="AB22" s="3">
-        <v>14000</v>
+        <v>20000</v>
       </c>
       <c r="AC22" s="3">
         <v>14000</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F23" s="3">
         <v>22000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>22000</v>
       </c>
-      <c r="F23" s="3">
-        <v>22400</v>
-      </c>
-      <c r="G23" s="3">
-        <v>22400</v>
-      </c>
       <c r="H23" s="3">
+        <v>18500</v>
+      </c>
+      <c r="I23" s="3">
+        <v>18500</v>
+      </c>
+      <c r="J23" s="3">
         <v>56500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>56500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>31300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>31300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>55500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>134800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>55200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>13800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>47400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>32300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>743000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>668000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>778000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>609000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>603000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>372000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>303000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>338000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>373000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>344000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>339000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>270000</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F24" s="3">
         <v>900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>900</v>
       </c>
-      <c r="F24" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-1500</v>
-      </c>
       <c r="H24" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J24" s="3">
         <v>3600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>3600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>2200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>2200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>4500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>10400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-22200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>2400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>8200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>4200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>188000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>169000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>174000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>155000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>155000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>101000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>74000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>127000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>142000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>130000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>123000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>85000</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2209,192 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F26" s="3">
         <v>21000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>21000</v>
       </c>
-      <c r="F26" s="3">
-        <v>23800</v>
-      </c>
-      <c r="G26" s="3">
-        <v>23800</v>
-      </c>
       <c r="H26" s="3">
+        <v>19600</v>
+      </c>
+      <c r="I26" s="3">
+        <v>19600</v>
+      </c>
+      <c r="J26" s="3">
         <v>52900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>52900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>29100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>29100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>51100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>124400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>77400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>11400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>39200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>28100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>555000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>499000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>604000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>454000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>448000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>271000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>229000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>211000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>231000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>214000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>216000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F27" s="3">
         <v>20300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>20300</v>
       </c>
-      <c r="F27" s="3">
-        <v>23200</v>
-      </c>
-      <c r="G27" s="3">
-        <v>23200</v>
-      </c>
       <c r="H27" s="3">
+        <v>19300</v>
+      </c>
+      <c r="I27" s="3">
+        <v>19300</v>
+      </c>
+      <c r="J27" s="3">
         <v>48300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>48300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>31400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>31400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>47300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>93100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>75300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>11400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>39200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>28100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>555000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>499000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>604000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>454000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>448000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>271000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>229000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>211000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>231000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>214000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>216000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2476,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2408,33 +2529,33 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>3000</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>68000</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2444,8 +2565,14 @@
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2654,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,80 +2743,86 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E32" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F32" s="3">
         <v>18700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>18700</v>
       </c>
-      <c r="F32" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>3200</v>
-      </c>
       <c r="H32" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="J32" s="3">
         <v>5700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>5700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>4300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>4300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>4500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-105400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-4500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-2400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-36500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-14800</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-14000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-2000</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>13000</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
@@ -2693,91 +2832,103 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F33" s="3">
         <v>21300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>21300</v>
       </c>
-      <c r="F33" s="3">
-        <v>20000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>20000</v>
-      </c>
       <c r="H33" s="3">
+        <v>16100</v>
+      </c>
+      <c r="I33" s="3">
+        <v>16100</v>
+      </c>
+      <c r="J33" s="3">
         <v>51500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>51500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>27500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>27500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>51200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>93100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>75300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>11400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>39200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>28100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>555000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>499000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>604000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>454000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>451000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>271000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>297000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>211000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>231000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>214000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>216000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +3010,197 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F35" s="3">
         <v>21300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>21300</v>
       </c>
-      <c r="F35" s="3">
-        <v>20000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>20000</v>
-      </c>
       <c r="H35" s="3">
+        <v>16100</v>
+      </c>
+      <c r="I35" s="3">
+        <v>16100</v>
+      </c>
+      <c r="J35" s="3">
         <v>51500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>51500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>27500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>27500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>51200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>93100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>75300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>11400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>39200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>28100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>555000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>499000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>604000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>454000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>451000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>271000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>297000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>211000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>231000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>214000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>216000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44104</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44012</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43830</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43738</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43646</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43646</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43555</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43465</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43373</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43190</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43008</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42916</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42825</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42735</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3230,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,91 +3263,99 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>62900</v>
+      </c>
+      <c r="F41" s="3">
         <v>78600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>78600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>120200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>120200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>161500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>161500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>138300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>138300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>17900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>647800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>147900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>128900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>122000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>112500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2953000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>2674000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>5117000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>2690000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1343000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1373000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1644000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1472000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2880000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>2231000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>1662000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1855000</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3187,47 +3366,47 @@
         <v>600</v>
       </c>
       <c r="F42" s="3">
+        <v>600</v>
+      </c>
+      <c r="G42" s="3">
+        <v>600</v>
+      </c>
+      <c r="H42" s="3">
         <v>1000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>1000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>218200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>218200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>186300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>186300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>196600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>1069900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>129500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>200400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>223100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>246000</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
       <c r="T42" s="3">
         <v>0</v>
       </c>
@@ -3258,91 +3437,103 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1427300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1427300</v>
+      </c>
+      <c r="F43" s="3">
         <v>1121800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1121800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1078300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1078300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>546800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>546800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>433900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>433900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>657400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>7495600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>894200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>569500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>446400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>670500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>23014000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>22790000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>21312000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>24445000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>24345000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>22709000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>20287000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>18796000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>15020000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>13393000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>13277000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>13397000</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3373,11 +3564,11 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -3424,142 +3615,154 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F45" s="3">
         <v>18500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>18500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>3000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>3000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>181200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>181200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>42400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1020900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>121300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>153000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>109800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>31900</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U45" s="3">
-        <v>0</v>
-      </c>
-      <c r="V45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+      <c r="X45" s="3">
         <v>4609000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>6863000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>10136000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>10446000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>7328000</v>
       </c>
-      <c r="AA45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>0</v>
-      </c>
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1494500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1494500</v>
+      </c>
+      <c r="F46" s="3">
         <v>1219400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1219400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1202700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1202700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1107800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1107800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>760900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>760900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>914300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>10234300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1292900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1051700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>901300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1060900</v>
       </c>
-      <c r="R46" s="3">
-        <v>0</v>
-      </c>
-      <c r="S46" s="3">
-        <v>0</v>
-      </c>
       <c r="T46" s="3">
         <v>0</v>
       </c>
@@ -3590,44 +3793,50 @@
       <c r="AC46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>164600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>164600</v>
+      </c>
+      <c r="F47" s="3">
         <v>93200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>93200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>95400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>95400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>243700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>243700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>195300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>195300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>185000</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3637,80 +3846,86 @@
       <c r="Q47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R47" s="3">
+      <c r="R47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T47" s="3">
         <v>1447000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>1053000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>993000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>640000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>682000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>901000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>692000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>1249000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>1154000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>9831000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>10187000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>9817000</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>291400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>291400</v>
+      </c>
+      <c r="F48" s="3">
         <v>271900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>271900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>70100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>70100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>242700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>242700</v>
       </c>
-      <c r="J48" s="3">
-        <v>0</v>
-      </c>
-      <c r="K48" s="3">
-        <v>0</v>
-      </c>
       <c r="L48" s="3">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3">
         <v>500</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
-      </c>
-      <c r="N48" s="3">
-        <v>0</v>
-      </c>
       <c r="O48" s="3">
         <v>0</v>
       </c>
@@ -3721,81 +3936,87 @@
         <v>0</v>
       </c>
       <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3">
         <v>833000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>812000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>797000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>792000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>778000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>801000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>780000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>752000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>592000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>555000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>531000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>526000</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>119400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>119400</v>
+      </c>
+      <c r="F49" s="3">
         <v>118700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>118700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>118400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>118400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>92700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>92700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>104500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>104500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>101500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>15200</v>
-      </c>
-      <c r="N49" s="3">
-        <v>1900</v>
-      </c>
-      <c r="O49" s="3">
-        <v>1900</v>
       </c>
       <c r="P49" s="3">
         <v>1900</v>
@@ -3804,43 +4025,49 @@
         <v>1900</v>
       </c>
       <c r="R49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="S49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="T49" s="3">
         <v>5463000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>5494000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>5525000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>5556000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>5561000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>5597000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>5629000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>5683000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>2985000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>3004000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>3023000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>3042000</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4149,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,8 +4238,14 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4034,15 +4273,15 @@
       <c r="K52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N52" s="3">
         <v>36300</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4052,24 +4291,24 @@
       <c r="Q52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R52" s="3">
+      <c r="R52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T52" s="3">
         <v>7124000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>5580000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>3185000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>3185000</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
       <c r="X52" s="3">
         <v>0</v>
       </c>
@@ -4088,8 +4327,14 @@
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4416,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2069900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2069900</v>
+      </c>
+      <c r="F54" s="3">
         <v>1703200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1703200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1486600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1486600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1687000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1687000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1060700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1060700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1237600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>10249500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1294800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1053700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>903200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1062800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>41119000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>38679000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>37191000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>37520000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>37511000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>38410000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>39412000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>38627000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>30110000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>29165000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>28834000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>28818000</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4542,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,225 +4575,239 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F57" s="3">
         <v>1300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>9400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>9400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>9500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>9500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>10600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>10600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>10500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>421900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>82300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>71100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>62400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>460100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>28833000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>26621000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>25139000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>26805000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>26859000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>27889000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>29119000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>28535000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>21821000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>21806000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>21582000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>21669000</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>64100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>64100</v>
+      </c>
+      <c r="F58" s="3">
         <v>30200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>30200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>99300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>99300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>66000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>66000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>20100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>20100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>20900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>232300</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>40500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>41000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>41100</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>96000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>97000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>318000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>147000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>97000</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>69200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>69200</v>
+      </c>
+      <c r="F59" s="3">
         <v>103000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>103000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>34200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>34200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>101100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>101100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>9200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>9200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>57400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>97800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>11200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>26300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>9700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>7500</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4544,11 +4817,11 @@
       <c r="V59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W59" s="3">
-        <v>0</v>
-      </c>
-      <c r="X59" s="3">
-        <v>0</v>
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y59" s="3">
         <v>0</v>
@@ -4565,59 +4838,65 @@
       <c r="AC59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>143100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>143100</v>
+      </c>
+      <c r="F60" s="3">
         <v>134500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>134500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>157100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>157100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>176700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>176700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>54500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>54500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>100900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>752000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>93500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>137900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>113100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>508800</v>
       </c>
-      <c r="R60" s="3">
-        <v>0</v>
-      </c>
-      <c r="S60" s="3">
-        <v>0</v>
-      </c>
       <c r="T60" s="3">
         <v>0</v>
       </c>
@@ -4648,22 +4927,28 @@
       <c r="AC60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>219400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>219400</v>
+      </c>
+      <c r="F61" s="3">
         <v>235100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>235100</v>
-      </c>
-      <c r="F61" s="3">
-        <v>30400</v>
-      </c>
-      <c r="G61" s="3">
-        <v>30400</v>
       </c>
       <c r="H61" s="3">
         <v>30400</v>
@@ -4672,82 +4957,88 @@
         <v>30400</v>
       </c>
       <c r="J61" s="3">
+        <v>30400</v>
+      </c>
+      <c r="K61" s="3">
+        <v>30400</v>
+      </c>
+      <c r="L61" s="3">
         <v>500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>500</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>101400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>12800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>12200</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>3574000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>3520000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>3484000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>2439000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>2456000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>2477000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2531000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>2555000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>2561000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>1765000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>1769000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>1817000</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F62" s="3">
         <v>1500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1500</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>5</v>
       </c>
@@ -4763,59 +5054,65 @@
       <c r="L62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O62" s="3">
         <v>20700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>33600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>31000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>25000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>219000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>215000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>211000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>177000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>163000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>131000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>182000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>193000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>268000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>269000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>284000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>281000</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5194,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5283,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5372,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>369900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>369900</v>
+      </c>
+      <c r="F66" s="3">
         <v>376700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>376700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>193000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>193000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>209800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>209800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>58300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>58300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>110700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>874000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>108900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>183700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>144000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>533700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>32626000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>30356000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>28834000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>29517000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>29575000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>30815000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>31979000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>31380000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>24650000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>23840000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>23635000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>23767000</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5498,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5583,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5672,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5761,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5850,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>906600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>906600</v>
+      </c>
+      <c r="F72" s="3">
         <v>900400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>900400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>859800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>859800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>809400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>809400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>712900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>712900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>661500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>7509200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>950700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>869900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>759100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>529100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>8194000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>7805000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>7475000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>7011000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>6673000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>6341000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>6189000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>6011000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>5895000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>5759000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>5640000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>5518000</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +6028,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +6117,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6206,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1591900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1591900</v>
+      </c>
+      <c r="F76" s="3">
         <v>1329900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1329900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1286500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1286500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1343300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1343300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>970700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>970700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1113500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>9375400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1185900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>870000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>759200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>529100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>8493000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>8323000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>8357000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>8003000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>7936000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>7595000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>7433000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>7247000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>5460000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>5325000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>5199000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>5051000</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6384,197 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44104</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44012</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43830</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43738</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43646</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43646</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43555</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43465</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43373</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43190</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43008</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42916</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42825</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42735</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F81" s="3">
         <v>21300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>21300</v>
       </c>
-      <c r="F81" s="3">
-        <v>20000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>20000</v>
-      </c>
       <c r="H81" s="3">
+        <v>16100</v>
+      </c>
+      <c r="I81" s="3">
+        <v>16100</v>
+      </c>
+      <c r="J81" s="3">
         <v>51500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>51500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>27500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>27500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>51200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>93100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>75300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>11400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>39200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>28100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>555000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>499000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>604000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>454000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>451000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>271000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>297000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>211000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>231000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>214000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>216000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,8 +6604,10 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6241,11 +6638,11 @@
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
@@ -6257,43 +6654,49 @@
         <v>0</v>
       </c>
       <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
         <v>69000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>67000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>66000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>70000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>69000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>72000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>72000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>50000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>44000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>44000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>43000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>45000</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6778,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6867,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6956,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +7045,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,8 +7134,14 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6739,11 +7172,11 @@
       <c r="L89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O89" s="3">
         <v>0</v>
@@ -6755,43 +7188,49 @@
         <v>0</v>
       </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>2438000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>573000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>2762000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1821000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>349000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>124000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-386000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>23000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>27000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>718000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-81000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>436000</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,8 +7260,10 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6853,11 +7294,11 @@
       <c r="L91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -6869,43 +7310,49 @@
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-59000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-48000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-44000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-63000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-47000</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-56000</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-63000</v>
       </c>
       <c r="Y91" s="3">
         <v>-56000</v>
       </c>
       <c r="Z91" s="3">
+        <v>-63000</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-62000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-100000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-27000</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7434,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,8 +7523,14 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7102,11 +7561,11 @@
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -7118,43 +7577,49 @@
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-195000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-48000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-426000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-66000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-35000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-440000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>633000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-1406000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-62000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-29000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-384000</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7649,10 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7216,11 +7683,11 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -7232,43 +7699,49 @@
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-166000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-169000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-168000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-120000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-119000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-119000</v>
       </c>
       <c r="X96" s="3">
         <v>-119000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-94000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-95000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-95000</v>
       </c>
       <c r="AB96" s="3">
         <v>-95000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7823,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7912,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,8 +8001,14 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7548,11 +8039,11 @@
       <c r="L100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
@@ -7564,43 +8055,49 @@
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>-409000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-552000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>594000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-408000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-344000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>45000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-75000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-37000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>685000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-97000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-74000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-114000</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7631,11 +8128,11 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -7682,8 +8179,14 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7714,11 +8217,11 @@
       <c r="L102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O102" s="3">
         <v>0</v>
@@ -7730,39 +8233,45 @@
         <v>0</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>1834000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-27000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>2930000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>1347000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-30000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-271000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>172000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-1408000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>649000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>569000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-193000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-62000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMTD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMTD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="92">
   <si>
     <t>AMTD</t>
   </si>
@@ -795,11 +795,11 @@
       <c r="E8" s="3">
         <v>18700</v>
       </c>
-      <c r="F8" s="3">
-        <v>14900</v>
-      </c>
-      <c r="G8" s="3">
-        <v>14900</v>
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H8" s="3">
         <v>8600</v>
@@ -807,8 +807,8 @@
       <c r="I8" s="3">
         <v>8600</v>
       </c>
-      <c r="J8" s="3">
-        <v>62200</v>
+      <c r="J8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K8" s="3">
         <v>62200</v>
@@ -973,11 +973,11 @@
       <c r="E10" s="3">
         <v>18700</v>
       </c>
-      <c r="F10" s="3">
-        <v>14900</v>
-      </c>
-      <c r="G10" s="3">
-        <v>14900</v>
+      <c r="F10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H10" s="3">
         <v>8600</v>
@@ -985,8 +985,8 @@
       <c r="I10" s="3">
         <v>8600</v>
       </c>
-      <c r="J10" s="3">
-        <v>62200</v>
+      <c r="J10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K10" s="3">
         <v>62200</v>
@@ -1363,10 +1363,10 @@
         <v>400</v>
       </c>
       <c r="F15" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>400</v>
@@ -1481,11 +1481,11 @@
       <c r="E17" s="3">
         <v>15700</v>
       </c>
-      <c r="F17" s="3">
-        <v>11600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>11600</v>
+      <c r="F17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H17" s="3">
         <v>16400</v>
@@ -1493,8 +1493,8 @@
       <c r="I17" s="3">
         <v>16400</v>
       </c>
-      <c r="J17" s="3">
-        <v>11400</v>
+      <c r="J17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K17" s="3">
         <v>11400</v>
@@ -1570,11 +1570,11 @@
       <c r="E18" s="3">
         <v>2900</v>
       </c>
-      <c r="F18" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G18" s="3">
-        <v>3200</v>
+      <c r="F18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H18" s="3">
         <v>-7800</v>
@@ -1582,8 +1582,8 @@
       <c r="I18" s="3">
         <v>-7800</v>
       </c>
-      <c r="J18" s="3">
-        <v>50800</v>
+      <c r="J18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K18" s="3">
         <v>50800</v>
@@ -1692,11 +1692,11 @@
       <c r="E20" s="3">
         <v>-2700</v>
       </c>
-      <c r="F20" s="3">
-        <v>-18700</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-18700</v>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H20" s="3">
         <v>9500</v>
@@ -1704,8 +1704,8 @@
       <c r="I20" s="3">
         <v>9500</v>
       </c>
-      <c r="J20" s="3">
-        <v>-5700</v>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K20" s="3">
         <v>-5700</v>
@@ -1782,10 +1782,10 @@
         <v>6100</v>
       </c>
       <c r="F21" s="3">
-        <v>22400</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>22400</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
         <v>-16900</v>
@@ -1794,7 +1794,7 @@
         <v>-17100</v>
       </c>
       <c r="J21" s="3">
-        <v>56500</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>56500</v>
@@ -1959,11 +1959,11 @@
       <c r="E23" s="3">
         <v>5700</v>
       </c>
-      <c r="F23" s="3">
-        <v>22000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>22000</v>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H23" s="3">
         <v>18500</v>
@@ -1971,8 +1971,8 @@
       <c r="I23" s="3">
         <v>18500</v>
       </c>
-      <c r="J23" s="3">
-        <v>56500</v>
+      <c r="J23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K23" s="3">
         <v>56500</v>
@@ -2048,11 +2048,11 @@
       <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
-        <v>900</v>
-      </c>
-      <c r="G24" s="3">
-        <v>900</v>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H24" s="3">
         <v>-1100</v>
@@ -2060,8 +2060,8 @@
       <c r="I24" s="3">
         <v>-1100</v>
       </c>
-      <c r="J24" s="3">
-        <v>3600</v>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K24" s="3">
         <v>3600</v>
@@ -2226,11 +2226,11 @@
       <c r="E26" s="3">
         <v>5800</v>
       </c>
-      <c r="F26" s="3">
-        <v>21000</v>
-      </c>
-      <c r="G26" s="3">
-        <v>21000</v>
+      <c r="F26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H26" s="3">
         <v>19600</v>
@@ -2238,8 +2238,8 @@
       <c r="I26" s="3">
         <v>19600</v>
       </c>
-      <c r="J26" s="3">
-        <v>52900</v>
+      <c r="J26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K26" s="3">
         <v>52900</v>
@@ -2315,11 +2315,11 @@
       <c r="E27" s="3">
         <v>5300</v>
       </c>
-      <c r="F27" s="3">
-        <v>20300</v>
-      </c>
-      <c r="G27" s="3">
-        <v>20300</v>
+      <c r="F27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H27" s="3">
         <v>19300</v>
@@ -2327,8 +2327,8 @@
       <c r="I27" s="3">
         <v>19300</v>
       </c>
-      <c r="J27" s="3">
-        <v>48300</v>
+      <c r="J27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K27" s="3">
         <v>48300</v>
@@ -2760,11 +2760,11 @@
       <c r="E32" s="3">
         <v>2700</v>
       </c>
-      <c r="F32" s="3">
-        <v>18700</v>
-      </c>
-      <c r="G32" s="3">
-        <v>18700</v>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H32" s="3">
         <v>-9500</v>
@@ -2772,8 +2772,8 @@
       <c r="I32" s="3">
         <v>-9500</v>
       </c>
-      <c r="J32" s="3">
-        <v>5700</v>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K32" s="3">
         <v>5700</v>
@@ -2849,11 +2849,11 @@
       <c r="E33" s="3">
         <v>4200</v>
       </c>
-      <c r="F33" s="3">
-        <v>21300</v>
-      </c>
-      <c r="G33" s="3">
-        <v>21300</v>
+      <c r="F33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H33" s="3">
         <v>16100</v>
@@ -2861,8 +2861,8 @@
       <c r="I33" s="3">
         <v>16100</v>
       </c>
-      <c r="J33" s="3">
-        <v>51500</v>
+      <c r="J33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K33" s="3">
         <v>51500</v>
@@ -3027,11 +3027,11 @@
       <c r="E35" s="3">
         <v>4200</v>
       </c>
-      <c r="F35" s="3">
-        <v>21300</v>
-      </c>
-      <c r="G35" s="3">
-        <v>21300</v>
+      <c r="F35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H35" s="3">
         <v>16100</v>
@@ -3039,8 +3039,8 @@
       <c r="I35" s="3">
         <v>16100</v>
       </c>
-      <c r="J35" s="3">
-        <v>51500</v>
+      <c r="J35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K35" s="3">
         <v>51500</v>
@@ -3276,11 +3276,11 @@
       <c r="E41" s="3">
         <v>62900</v>
       </c>
-      <c r="F41" s="3">
-        <v>78600</v>
-      </c>
-      <c r="G41" s="3">
-        <v>78600</v>
+      <c r="F41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H41" s="3">
         <v>120200</v>
@@ -3288,8 +3288,8 @@
       <c r="I41" s="3">
         <v>120200</v>
       </c>
-      <c r="J41" s="3">
-        <v>161500</v>
+      <c r="J41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K41" s="3">
         <v>161500</v>
@@ -3366,10 +3366,10 @@
         <v>600</v>
       </c>
       <c r="F42" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>1000</v>
@@ -3378,7 +3378,7 @@
         <v>1000</v>
       </c>
       <c r="J42" s="3">
-        <v>218200</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>218200</v>
@@ -3454,11 +3454,11 @@
       <c r="E43" s="3">
         <v>1427300</v>
       </c>
-      <c r="F43" s="3">
-        <v>1121800</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1121800</v>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H43" s="3">
         <v>1078300</v>
@@ -3466,8 +3466,8 @@
       <c r="I43" s="3">
         <v>1078300</v>
       </c>
-      <c r="J43" s="3">
-        <v>546800</v>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>546800</v>
@@ -3632,11 +3632,11 @@
       <c r="E45" s="3">
         <v>3700</v>
       </c>
-      <c r="F45" s="3">
-        <v>18500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>18500</v>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H45" s="3">
         <v>3000</v>
@@ -3644,8 +3644,8 @@
       <c r="I45" s="3">
         <v>3000</v>
       </c>
-      <c r="J45" s="3">
-        <v>181200</v>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K45" s="3">
         <v>181200</v>
@@ -3721,11 +3721,11 @@
       <c r="E46" s="3">
         <v>1494500</v>
       </c>
-      <c r="F46" s="3">
-        <v>1219400</v>
-      </c>
-      <c r="G46" s="3">
-        <v>1219400</v>
+      <c r="F46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H46" s="3">
         <v>1202700</v>
@@ -3733,8 +3733,8 @@
       <c r="I46" s="3">
         <v>1202700</v>
       </c>
-      <c r="J46" s="3">
-        <v>1107800</v>
+      <c r="J46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K46" s="3">
         <v>1107800</v>
@@ -3810,11 +3810,11 @@
       <c r="E47" s="3">
         <v>164600</v>
       </c>
-      <c r="F47" s="3">
-        <v>93200</v>
-      </c>
-      <c r="G47" s="3">
-        <v>93200</v>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H47" s="3">
         <v>95400</v>
@@ -3822,8 +3822,8 @@
       <c r="I47" s="3">
         <v>95400</v>
       </c>
-      <c r="J47" s="3">
-        <v>243700</v>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K47" s="3">
         <v>243700</v>
@@ -3899,11 +3899,11 @@
       <c r="E48" s="3">
         <v>291400</v>
       </c>
-      <c r="F48" s="3">
-        <v>271900</v>
-      </c>
-      <c r="G48" s="3">
-        <v>271900</v>
+      <c r="F48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H48" s="3">
         <v>70100</v>
@@ -3911,8 +3911,8 @@
       <c r="I48" s="3">
         <v>70100</v>
       </c>
-      <c r="J48" s="3">
-        <v>242700</v>
+      <c r="J48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K48" s="3">
         <v>242700</v>
@@ -3988,11 +3988,11 @@
       <c r="E49" s="3">
         <v>119400</v>
       </c>
-      <c r="F49" s="3">
-        <v>118700</v>
-      </c>
-      <c r="G49" s="3">
-        <v>118700</v>
+      <c r="F49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H49" s="3">
         <v>118400</v>
@@ -4000,8 +4000,8 @@
       <c r="I49" s="3">
         <v>118400</v>
       </c>
-      <c r="J49" s="3">
-        <v>92700</v>
+      <c r="J49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K49" s="3">
         <v>92700</v>
@@ -4433,11 +4433,11 @@
       <c r="E54" s="3">
         <v>2069900</v>
       </c>
-      <c r="F54" s="3">
-        <v>1703200</v>
-      </c>
-      <c r="G54" s="3">
-        <v>1703200</v>
+      <c r="F54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H54" s="3">
         <v>1486600</v>
@@ -4445,8 +4445,8 @@
       <c r="I54" s="3">
         <v>1486600</v>
       </c>
-      <c r="J54" s="3">
-        <v>1687000</v>
+      <c r="J54" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K54" s="3">
         <v>1687000</v>
@@ -4588,11 +4588,11 @@
       <c r="E57" s="3">
         <v>3600</v>
       </c>
-      <c r="F57" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1300</v>
+      <c r="F57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H57" s="3">
         <v>9400</v>
@@ -4600,8 +4600,8 @@
       <c r="I57" s="3">
         <v>9400</v>
       </c>
-      <c r="J57" s="3">
-        <v>9500</v>
+      <c r="J57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K57" s="3">
         <v>9500</v>
@@ -4677,11 +4677,11 @@
       <c r="E58" s="3">
         <v>64100</v>
       </c>
-      <c r="F58" s="3">
-        <v>30200</v>
-      </c>
-      <c r="G58" s="3">
-        <v>30200</v>
+      <c r="F58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H58" s="3">
         <v>99300</v>
@@ -4689,8 +4689,8 @@
       <c r="I58" s="3">
         <v>99300</v>
       </c>
-      <c r="J58" s="3">
-        <v>66000</v>
+      <c r="J58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K58" s="3">
         <v>66000</v>
@@ -4766,11 +4766,11 @@
       <c r="E59" s="3">
         <v>69200</v>
       </c>
-      <c r="F59" s="3">
-        <v>103000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>103000</v>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H59" s="3">
         <v>34200</v>
@@ -4778,8 +4778,8 @@
       <c r="I59" s="3">
         <v>34200</v>
       </c>
-      <c r="J59" s="3">
-        <v>101100</v>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K59" s="3">
         <v>101100</v>
@@ -4855,11 +4855,11 @@
       <c r="E60" s="3">
         <v>143100</v>
       </c>
-      <c r="F60" s="3">
-        <v>134500</v>
-      </c>
-      <c r="G60" s="3">
-        <v>134500</v>
+      <c r="F60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H60" s="3">
         <v>157100</v>
@@ -4867,8 +4867,8 @@
       <c r="I60" s="3">
         <v>157100</v>
       </c>
-      <c r="J60" s="3">
-        <v>176700</v>
+      <c r="J60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K60" s="3">
         <v>176700</v>
@@ -4945,10 +4945,10 @@
         <v>219400</v>
       </c>
       <c r="F61" s="3">
-        <v>235100</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>235100</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>30400</v>
@@ -4957,7 +4957,7 @@
         <v>30400</v>
       </c>
       <c r="J61" s="3">
-        <v>30400</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>30400</v>
@@ -5033,11 +5033,11 @@
       <c r="E62" s="3">
         <v>1700</v>
       </c>
-      <c r="F62" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1500</v>
+      <c r="F62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>5</v>
@@ -5389,11 +5389,11 @@
       <c r="E66" s="3">
         <v>369900</v>
       </c>
-      <c r="F66" s="3">
-        <v>376700</v>
-      </c>
-      <c r="G66" s="3">
-        <v>376700</v>
+      <c r="F66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H66" s="3">
         <v>193000</v>
@@ -5401,8 +5401,8 @@
       <c r="I66" s="3">
         <v>193000</v>
       </c>
-      <c r="J66" s="3">
-        <v>209800</v>
+      <c r="J66" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K66" s="3">
         <v>209800</v>
@@ -5867,11 +5867,11 @@
       <c r="E72" s="3">
         <v>906600</v>
       </c>
-      <c r="F72" s="3">
-        <v>900400</v>
-      </c>
-      <c r="G72" s="3">
-        <v>900400</v>
+      <c r="F72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H72" s="3">
         <v>859800</v>
@@ -5879,8 +5879,8 @@
       <c r="I72" s="3">
         <v>859800</v>
       </c>
-      <c r="J72" s="3">
-        <v>809400</v>
+      <c r="J72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K72" s="3">
         <v>809400</v>
@@ -6223,11 +6223,11 @@
       <c r="E76" s="3">
         <v>1591900</v>
       </c>
-      <c r="F76" s="3">
-        <v>1329900</v>
-      </c>
-      <c r="G76" s="3">
-        <v>1329900</v>
+      <c r="F76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H76" s="3">
         <v>1286500</v>
@@ -6235,8 +6235,8 @@
       <c r="I76" s="3">
         <v>1286500</v>
       </c>
-      <c r="J76" s="3">
-        <v>1343300</v>
+      <c r="J76" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K76" s="3">
         <v>1343300</v>
@@ -6495,11 +6495,11 @@
       <c r="E81" s="3">
         <v>4200</v>
       </c>
-      <c r="F81" s="3">
-        <v>21300</v>
-      </c>
-      <c r="G81" s="3">
-        <v>21300</v>
+      <c r="F81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H81" s="3">
         <v>16100</v>
@@ -6507,8 +6507,8 @@
       <c r="I81" s="3">
         <v>16100</v>
       </c>
-      <c r="J81" s="3">
-        <v>51500</v>
+      <c r="J81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K81" s="3">
         <v>51500</v>

--- a/AAII_Financials/Quarterly/AMTD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMTD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
   <si>
     <t>AMTD</t>
   </si>
@@ -656,222 +656,234 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F8" s="3">
         <v>18700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>18700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="3">
         <v>8600</v>
       </c>
-      <c r="G8" s="3">
-        <v>8600</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>28700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>28400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>58600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>62200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>28400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>28400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>58600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>83900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>69100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>20100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>18500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>25000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1491000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1451000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1516000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1398000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1382000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1415000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>1257000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>983000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>931000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>904000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>859000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>830000</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -923,21 +935,21 @@
       <c r="S9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T9" s="3">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>59000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>53000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>49000</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>5</v>
       </c>
@@ -959,50 +971,56 @@
       <c r="AE9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F10" s="3">
         <v>18700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>18700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="I10" s="3">
         <v>8600</v>
       </c>
-      <c r="G10" s="3">
-        <v>8600</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>28700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>28400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>58600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>62200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>28400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>28400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>58600</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1012,21 +1030,21 @@
       <c r="S10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>1432000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>1398000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1467000</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1048,8 +1066,14 @@
       <c r="AE10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1081,22 +1105,24 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
-        <v>100</v>
-      </c>
-      <c r="E12" s="3">
-        <v>100</v>
-      </c>
-      <c r="F12" s="3">
-        <v>400</v>
-      </c>
-      <c r="G12" s="3">
-        <v>400</v>
+      <c r="D12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H12" s="3">
         <v>-400</v>
@@ -1104,23 +1130,23 @@
       <c r="I12" s="3">
         <v>400</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L12" s="3">
+      <c r="J12" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K12" s="3">
         <v>400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N12" s="3">
         <v>400</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>5</v>
+      <c r="O12" s="3">
+        <v>400</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>5</v>
@@ -1170,8 +1196,14 @@
       <c r="AE12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1259,47 +1291,53 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="F14" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="H14" s="3">
         <v>-35800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-35800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-10700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-10700</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>-10700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-10700</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1312,68 +1350,74 @@
       <c r="S14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>-60000</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3">
         <v>1000</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>1000</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E15" s="3">
         <v>1600</v>
       </c>
-      <c r="E15" s="3">
-        <v>400</v>
-      </c>
       <c r="F15" s="3">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="G15" s="3">
+        <v>700</v>
+      </c>
+      <c r="H15" s="3">
+        <v>700</v>
+      </c>
+      <c r="I15" s="3">
         <v>200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>200</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
@@ -1402,43 +1446,49 @@
         <v>0</v>
       </c>
       <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
         <v>69000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>67000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>66000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>70000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>69000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>72000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>72000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>50000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>44000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>44000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>43000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>45000</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1467,186 +1517,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>14200</v>
+      </c>
+      <c r="F17" s="3">
         <v>15700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>15700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
+        <v>15100</v>
+      </c>
+      <c r="I17" s="3">
         <v>16400</v>
       </c>
-      <c r="G17" s="3">
-        <v>16400</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>12200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>12100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>7600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>11400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>12100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>12100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>7600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>51500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>16500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>7300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>6900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>6900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>711000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>746000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>720000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>764000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>751000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1019000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>921000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>622000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>538000</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>546000</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>506000</v>
       </c>
       <c r="AE17" s="3">
         <v>546000</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3">
+        <v>506000</v>
+      </c>
+      <c r="AG17" s="3">
+        <v>546000</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="F18" s="3">
         <v>2900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>2900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="I18" s="3">
         <v>-7800</v>
       </c>
-      <c r="G18" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>16500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>16300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>51000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>50800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>16300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>16300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>51000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>32400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>52600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>12900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>11600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>18200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>780000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>705000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>796000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>634000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>631000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>396000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>336000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>361000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>393000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>358000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>353000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>284000</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1678,86 +1742,88 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2700</v>
+        <v>-9400</v>
       </c>
       <c r="E20" s="3">
-        <v>-2700</v>
+        <v>-9400</v>
       </c>
       <c r="F20" s="3">
+        <v>9700</v>
+      </c>
+      <c r="G20" s="3">
+        <v>9700</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="I20" s="3">
         <v>9500</v>
       </c>
-      <c r="G20" s="3">
-        <v>9500</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-4400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-4300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-4500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-5700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-4300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-4300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-4500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>105400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>4500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>2400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>36500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>14800</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>14000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>2000</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-13000</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
@@ -1767,97 +1833,109 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>7300</v>
+        <v>900</v>
       </c>
       <c r="E21" s="3">
-        <v>6100</v>
+        <v>100</v>
       </c>
       <c r="F21" s="3">
-        <v>-16900</v>
+        <v>-5100</v>
       </c>
       <c r="G21" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="I21" s="3">
         <v>-17100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>21100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>20600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>55500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>56500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>20600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>20600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>55500</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="3">
         <v>15300</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>849000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>772000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>876000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>706000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>700000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>468000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>395000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>411000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>437000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>402000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>396000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>329000</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1894,237 +1972,255 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="3">
         <v>3000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>1900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>1500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>37000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>37000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>32000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>27000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>28000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>24000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>20000</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>23000</v>
       </c>
       <c r="AB22" s="3">
         <v>20000</v>
       </c>
       <c r="AC22" s="3">
-        <v>14000</v>
+        <v>23000</v>
       </c>
       <c r="AD22" s="3">
-        <v>14000</v>
+        <v>20000</v>
       </c>
       <c r="AE22" s="3">
         <v>14000</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F23" s="3">
         <v>5700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>5700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
+        <v>26200</v>
+      </c>
+      <c r="I23" s="3">
         <v>18500</v>
       </c>
-      <c r="G23" s="3">
-        <v>18500</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>31600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>31300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>55500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>56500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>31300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>31300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>55500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>134800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>55200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>13800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>47400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>32300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>743000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>668000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>778000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>609000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>603000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>372000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>303000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>338000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>373000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>344000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>339000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>270000</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="I24" s="3">
         <v>-1100</v>
       </c>
-      <c r="G24" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>2300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>2200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>4500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>3600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>2200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>2200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>4500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>10400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>2400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>8200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>4200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>188000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>169000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>174000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>155000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>155000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>101000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>74000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>127000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>142000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>130000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>123000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>85000</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2212,186 +2308,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F26" s="3">
         <v>5800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>5800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
+        <v>28100</v>
+      </c>
+      <c r="I26" s="3">
         <v>19600</v>
       </c>
-      <c r="G26" s="3">
-        <v>19600</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>29300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>29100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>51100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>52900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>29100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>29100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>51100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>124400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>77400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>11400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>39200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>28100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>555000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>499000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>604000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>454000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>448000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>271000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>229000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>211000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>231000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>214000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>216000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>5300</v>
+        <v>-900</v>
       </c>
       <c r="E27" s="3">
-        <v>5300</v>
+        <v>-900</v>
       </c>
       <c r="F27" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G27" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H27" s="3">
+        <v>18600</v>
+      </c>
+      <c r="I27" s="3">
         <v>19300</v>
       </c>
-      <c r="G27" s="3">
-        <v>19300</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>31600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>31400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>47300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>48300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>31400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>31400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>47300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>93100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>75300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>11400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>39200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>28100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>555000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>499000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>604000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>454000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>448000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>271000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>229000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>211000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>231000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>214000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>216000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2479,8 +2593,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2532,33 +2652,33 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>3000</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>68000</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2568,8 +2688,14 @@
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2657,8 +2783,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2746,86 +2878,92 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2700</v>
+        <v>9400</v>
       </c>
       <c r="E32" s="3">
-        <v>2700</v>
+        <v>9400</v>
       </c>
       <c r="F32" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="H32" s="3">
+        <v>15800</v>
+      </c>
+      <c r="I32" s="3">
         <v>-9500</v>
       </c>
-      <c r="G32" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>4400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>4300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>4500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>5700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>4300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>4300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>4500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-105400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-2400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-36500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-14800</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-14000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-2000</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>13000</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
@@ -2835,97 +2973,109 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F33" s="3">
         <v>4200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>4200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
+        <v>23900</v>
+      </c>
+      <c r="I33" s="3">
         <v>16100</v>
       </c>
-      <c r="G33" s="3">
-        <v>16100</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>27700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>27500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>51200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>51500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>27500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>27500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>51200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>93100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>75300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>11400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>39200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>28100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>555000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>499000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>604000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>454000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>451000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>271000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>297000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>211000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>231000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>214000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>216000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3013,191 +3163,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F35" s="3">
         <v>4200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>4200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
+        <v>23900</v>
+      </c>
+      <c r="I35" s="3">
         <v>16100</v>
       </c>
-      <c r="G35" s="3">
-        <v>16100</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>27700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>27500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>51200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>51500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>27500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>27500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>51200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>93100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>75300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>11400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>39200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>28100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>555000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>499000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>604000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>454000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>451000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>271000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>297000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>211000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>231000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>214000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>216000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3229,8 +3397,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3262,154 +3432,162 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>51100</v>
+      </c>
+      <c r="F41" s="3">
         <v>62900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>62900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>120200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>120200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>138300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>138300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>17900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>161500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>138300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>138300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>17900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>647800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>147900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>128900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>122000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>112500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2953000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>2674000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>5117000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>2690000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1343000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1373000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1644000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1472000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>2880000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>2231000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>1662000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>1855000</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>1000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>1000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>186300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>186300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>196600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>218200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>186300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>186300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>196600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>1069900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>129500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>200400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>223100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>246000</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
-      <c r="U42" s="3">
-        <v>0</v>
-      </c>
       <c r="V42" s="3">
         <v>0</v>
       </c>
@@ -3440,97 +3618,109 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1372700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1372700</v>
+      </c>
+      <c r="F43" s="3">
         <v>1427300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1427300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1078300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1078300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>433900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>433900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>657400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>546800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>433900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>433900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>657400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>7495600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>894200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>569500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>446400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>670500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>23014000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>22790000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>21312000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>24445000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>24345000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>22709000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>20287000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>18796000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>15020000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>13393000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>13277000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>13397000</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3567,11 +3757,11 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3618,154 +3808,166 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F45" s="3">
         <v>3700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>3000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>3000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>42400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>181200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>42400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1020900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>121300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>153000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>109800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>31900</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
-      <c r="X45" s="3">
+      <c r="W45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3">
         <v>4609000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>6863000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>10136000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>10446000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>7328000</v>
       </c>
-      <c r="AC45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>0</v>
-      </c>
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1426200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1426200</v>
+      </c>
+      <c r="F46" s="3">
         <v>1494500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1494500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1202700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1202700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>760900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>760900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>914300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1107800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>760900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>760900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>914300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>10234300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1292900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1051700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>901300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1060900</v>
       </c>
-      <c r="T46" s="3">
-        <v>0</v>
-      </c>
-      <c r="U46" s="3">
-        <v>0</v>
-      </c>
       <c r="V46" s="3">
         <v>0</v>
       </c>
@@ -3796,50 +3998,56 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>358400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>358400</v>
+      </c>
+      <c r="F47" s="3">
         <v>164600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>164600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>95400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>95400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>195300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>195300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>185000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>243700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>195300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>195300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>185000</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3849,86 +4057,92 @@
       <c r="S47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T47" s="3">
+      <c r="T47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V47" s="3">
         <v>1447000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>1053000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>993000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>640000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>682000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>901000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>692000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>1249000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>1154000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>9831000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>10187000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>9817000</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>314100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>314100</v>
+      </c>
+      <c r="F48" s="3">
         <v>291400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>291400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>70100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>70100</v>
       </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
       <c r="J48" s="3">
+        <v>0</v>
+      </c>
+      <c r="K48" s="3">
+        <v>0</v>
+      </c>
+      <c r="L48" s="3">
         <v>500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>242700</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
-      </c>
-      <c r="M48" s="3">
-        <v>0</v>
-      </c>
       <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3">
         <v>500</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
-      </c>
-      <c r="P48" s="3">
-        <v>0</v>
-      </c>
       <c r="Q48" s="3">
         <v>0</v>
       </c>
@@ -3939,87 +4153,93 @@
         <v>0</v>
       </c>
       <c r="T48" s="3">
+        <v>0</v>
+      </c>
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+      <c r="V48" s="3">
         <v>833000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>812000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>797000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>792000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>778000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>801000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>780000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>752000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>592000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>555000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>531000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>526000</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>119100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>119100</v>
+      </c>
+      <c r="F49" s="3">
         <v>119400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>119400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>118400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>118400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>104500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>104500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>101500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>92700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>104500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>104500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>101500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>15200</v>
-      </c>
-      <c r="P49" s="3">
-        <v>1900</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>1900</v>
       </c>
       <c r="R49" s="3">
         <v>1900</v>
@@ -4028,43 +4248,49 @@
         <v>1900</v>
       </c>
       <c r="T49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="U49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="V49" s="3">
         <v>5463000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>5494000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>5525000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>5556000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>5561000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>5597000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>5629000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>5683000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>2985000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>3004000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>3023000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>3042000</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4152,8 +4378,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4241,16 +4473,22 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>5</v>
+      <c r="D52" s="3">
+        <v>82600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>82600</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>5</v>
@@ -4264,27 +4502,27 @@
       <c r="I52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L52" s="3">
         <v>36300</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P52" s="3">
         <v>36300</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4294,24 +4532,24 @@
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T52" s="3">
+      <c r="T52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V52" s="3">
         <v>7124000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>5580000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>3185000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>3185000</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>0</v>
-      </c>
       <c r="Z52" s="3">
         <v>0</v>
       </c>
@@ -4330,8 +4568,14 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4419,97 +4663,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2300300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2300300</v>
+      </c>
+      <c r="F54" s="3">
         <v>2069900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2069900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1486600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1486600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1060700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1060700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1237600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1687000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1060700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1060700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1237600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>10249500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1294800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1053700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>903200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1062800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>41119000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>38679000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>37191000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>37520000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>37511000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>38410000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>39412000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>38627000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>30110000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>29165000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>28834000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>28818000</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4541,8 +4797,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4574,243 +4832,257 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F57" s="3">
         <v>3600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>9400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>9400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>10600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>10600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>10500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>9500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>10600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>10600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>10500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>421900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>82300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>71100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>62400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>460100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>28833000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>26621000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>25139000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>26805000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>26859000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>27889000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>29119000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>28535000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>21821000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>21806000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>21582000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>21669000</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>83500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>83500</v>
+      </c>
+      <c r="F58" s="3">
         <v>64100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>64100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>99300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>99300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>20100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>20100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>20900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>66000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>20100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>20100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>20900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>232300</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>40500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>41000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>41100</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
       <c r="V58" s="3">
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>96000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>97000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>318000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>147000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>97000</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>68100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>68100</v>
+      </c>
+      <c r="F59" s="3">
         <v>69200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>69200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>34200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>34200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>9200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>9200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>57400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>101100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>9200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>9200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>57400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>97800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>11200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>26300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>9700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>7500</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4820,11 +5092,11 @@
       <c r="X59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>0</v>
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA59" s="3">
         <v>0</v>
@@ -4841,65 +5113,71 @@
       <c r="AE59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>162400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>162400</v>
+      </c>
+      <c r="F60" s="3">
         <v>143100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>143100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>157100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>157100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>54500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>54500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>100900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>176700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>54500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>54500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>100900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>752000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>93500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>137900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>113100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>508800</v>
       </c>
-      <c r="T60" s="3">
-        <v>0</v>
-      </c>
-      <c r="U60" s="3">
-        <v>0</v>
-      </c>
       <c r="V60" s="3">
         <v>0</v>
       </c>
@@ -4930,112 +5208,124 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>208900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>208900</v>
+      </c>
+      <c r="F61" s="3">
         <v>219400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>219400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>30400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>30400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>500</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>30400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>500</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>101400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>12800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>12200</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>3574000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>3520000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>3484000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>2439000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2456000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>2477000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>2531000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>2555000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>2561000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>1765000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>1769000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>1817000</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>158500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>158500</v>
+      </c>
+      <c r="F62" s="3">
         <v>1700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1700</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>5</v>
       </c>
@@ -5057,59 +5347,65 @@
       <c r="N62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q62" s="3">
         <v>20700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>33600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>31000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>25000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>219000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>215000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>211000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>177000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>163000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>131000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>182000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>193000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>268000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>269000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>284000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>281000</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5197,8 +5493,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5286,8 +5588,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5375,97 +5683,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>535500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>535500</v>
+      </c>
+      <c r="F66" s="3">
         <v>369900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>369900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>193000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>193000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>58300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>58300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>110700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>209800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>58300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>58300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>110700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>874000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>108900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>183700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>144000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>533700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>32626000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>30356000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>28834000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>29517000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>29575000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>30815000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>31979000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>31380000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>24650000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>23840000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>23635000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>23767000</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5497,8 +5817,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5586,8 +5908,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5675,8 +6003,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5764,8 +6098,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5853,97 +6193,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>940700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>940700</v>
+      </c>
+      <c r="F72" s="3">
         <v>906600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>906600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>859800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>859800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>712900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>712900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>661500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>809400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>712900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>712900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>661500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>7509200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>950700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>869900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>759100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>529100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>8194000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>7805000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>7475000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>7011000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>6673000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>6341000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>6189000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>6011000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>5895000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>5759000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>5640000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>5518000</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6031,8 +6383,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6120,8 +6478,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6209,97 +6573,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1587700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1587700</v>
+      </c>
+      <c r="F76" s="3">
         <v>1591900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1591900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1286500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1286500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>970700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>970700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1113500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1343300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>970700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>970700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1113500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>9375400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1185900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>870000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>759200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>529100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>8493000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>8323000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>8357000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>8003000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>7936000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>7595000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>7433000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>7247000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>5460000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>5325000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>5199000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>5051000</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6387,191 +6763,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F81" s="3">
         <v>4200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>4200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
+        <v>23900</v>
+      </c>
+      <c r="I81" s="3">
         <v>16100</v>
       </c>
-      <c r="G81" s="3">
-        <v>16100</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>27700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>27500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>51200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>51500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>27500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>27500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>51200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>93100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>75300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>11400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>39200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>28100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>555000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>499000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>604000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>454000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>451000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>271000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>297000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>211000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>231000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>214000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>216000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6603,8 +6997,10 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6641,11 +7037,11 @@
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -6657,43 +7053,49 @@
         <v>0</v>
       </c>
       <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
         <v>69000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>67000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>66000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>70000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>69000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>72000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>72000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>50000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>44000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>44000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>43000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>45000</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6781,8 +7183,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6870,8 +7278,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6959,8 +7373,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7048,8 +7468,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7137,8 +7563,14 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7175,11 +7607,11 @@
       <c r="N89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3">
-        <v>0</v>
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q89" s="3">
         <v>0</v>
@@ -7191,43 +7623,49 @@
         <v>0</v>
       </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>2438000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>573000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>2762000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1821000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>349000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>124000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-386000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>23000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>27000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>718000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-81000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>436000</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7259,8 +7697,10 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7297,11 +7737,11 @@
       <c r="N91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -7313,43 +7753,49 @@
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-59000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-48000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-44000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-63000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-47000</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-56000</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-63000</v>
       </c>
       <c r="AA91" s="3">
         <v>-56000</v>
       </c>
       <c r="AB91" s="3">
+        <v>-63000</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-62000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-100000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-27000</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7437,8 +7883,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7526,8 +7978,14 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7564,11 +8022,11 @@
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -7580,43 +8038,49 @@
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-195000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-48000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-426000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-66000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-35000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-440000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>633000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-1406000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-62000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-29000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-384000</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7648,8 +8112,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7686,11 +8152,11 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7702,43 +8168,49 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-166000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-169000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-168000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-120000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-119000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-119000</v>
       </c>
       <c r="Z96" s="3">
         <v>-119000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-94000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-95000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-95000</v>
       </c>
       <c r="AD96" s="3">
         <v>-95000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7826,8 +8298,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7915,8 +8393,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8004,8 +8488,14 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8042,11 +8532,11 @@
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
@@ -8058,43 +8548,49 @@
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-409000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-552000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>594000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-408000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-344000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>45000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-75000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-37000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>685000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-97000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-74000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-114000</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8131,11 +8627,11 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8182,8 +8678,14 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8208,11 +8710,11 @@
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>5</v>
@@ -8220,11 +8722,11 @@
       <c r="N102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3">
-        <v>0</v>
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q102" s="3">
         <v>0</v>
@@ -8236,39 +8738,45 @@
         <v>0</v>
       </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>1834000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-27000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>2930000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>1347000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-30000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-271000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>172000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-1408000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>649000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>569000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-193000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-62000</v>
       </c>
     </row>
